--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,10 +2801,8 @@
           <t>나라스페이스테크놀로지</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>478340</t>
-        </is>
+      <c r="E17" t="n">
+        <v>478340</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2867,10 +2865,8 @@
           <t>14050,14030,13920,13640,14340</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y17" t="n">
+        <v>6</v>
       </c>
       <c r="Z17" t="n">
         <v>-19000</v>
@@ -2948,10 +2944,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E18" t="n">
+        <v>47040</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3014,10 +3008,8 @@
           <t>17700,18620,17640,17730,17830</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y18" t="n">
+        <v>3</v>
       </c>
       <c r="Z18" t="n">
         <v>-66000</v>
@@ -3095,10 +3087,8 @@
           <t>코스모로보틱스</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>439960</t>
-        </is>
+      <c r="E19" t="n">
+        <v>439960</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3161,10 +3151,8 @@
           <t>11440,11390,7940,7520,8630</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y19" t="n">
+        <v>-7</v>
       </c>
       <c r="Z19" t="n">
         <v>-238000</v>
@@ -3220,6 +3208,737 @@
       <c r="AQ19" t="inlineStr">
         <is>
           <t>분식회계 의혹 및 검찰 수사 관련 부정적 언급 다수. 거래 정지 가능성 및 투자 경고 메시지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>41</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="L20" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>47700</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>+17.92%</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>4713633</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>226003292475</v>
+      </c>
+      <c r="R20" t="n">
+        <v>132.01</v>
+      </c>
+      <c r="S20" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>609</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.2804530679266781</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>39700,40950,41350,40200,40650</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>477000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="n">
+        <v>-28.44</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>63536</v>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>HLB 간암 신약 美 FDA 승인 기대감 고조. VAI 공시 및 블로그 통해 결과 확인, 로슈 제치고 간암 치료제 시장 선도 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>엑스게이트</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>356680</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>41</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="L21" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>20550</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>+9.37%</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>5966898</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>126789208715</v>
+      </c>
+      <c r="R21" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U21" t="n">
+        <v>107</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.6825931441455234</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>18630,18550,17890,18300,19260</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>-64000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="n">
+        <v>146.79</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1557</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>30550</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>6100</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>5866</v>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>보안 관련 정부 점검 지시에 따른 보안주 상승 기대감. 엑스게이트는 금융 고객사 207곳 보유.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>41</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="L22" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>271750</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-1.54%</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>6179397</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1706163262750</v>
+      </c>
+      <c r="R22" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="S22" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>771</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.5241715874700386</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>270000,275000,269500,274500,276000</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>-779000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>311000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-56.11</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>90200</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>15887262</v>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>반도체 시장 급등 랠리 및 엔비디아 신고가 경신 등 호재 언급. 다만, 마이크론 하락 및 감정적 기대감 위주의 내용으로 fact_score는 보수적으로 산정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>글로벌테크놀로지</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>486510</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>41</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="L23" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>15810</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>+3.00%</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>3410770</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>53622836810</v>
+      </c>
+      <c r="R23" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="U23" t="n">
+        <v>90</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>6.61782999308915</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>14500,18230,16250,14860</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>14000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>29750</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>12760</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>3106</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>기타법인 자사주 매집 및 통신 광원 반도체 기술 보유. 회사 차원 공식 발표는 부재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>41</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="L24" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>1789000</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>-2.82%</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1282632</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2318642860500</v>
+      </c>
+      <c r="R24" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="S24" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>800</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.6068043499950114</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>1761000,1790000,1783000,1828000,1842000</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>-331000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-20.65</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>403000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13068508</v>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>오너리스크 및 솔리다임 상장 이슈로 인한 SK하이닉스 주가 하락 우려. HBM 경쟁력 약화 지적.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ24"/>
+  <dimension ref="A1:AQ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3230,10 +3230,8 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>028300</t>
-        </is>
+      <c r="E20" t="n">
+        <v>28300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3296,10 +3294,8 @@
           <t>39700,40950,41350,40200,40650</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y20" t="n">
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
         <v>477000</v>
@@ -3377,10 +3373,8 @@
           <t>엑스게이트</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>356680</t>
-        </is>
+      <c r="E21" t="n">
+        <v>356680</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3443,10 +3437,8 @@
           <t>18630,18550,17890,18300,19260</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y21" t="n">
+        <v>5</v>
       </c>
       <c r="Z21" t="n">
         <v>-64000</v>
@@ -3524,10 +3516,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E22" t="n">
+        <v>5930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3590,10 +3580,8 @@
           <t>270000,275000,269500,274500,276000</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y22" t="n">
+        <v>2</v>
       </c>
       <c r="Z22" t="n">
         <v>-779000</v>
@@ -3671,10 +3659,8 @@
           <t>글로벌테크놀로지</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>486510</t>
-        </is>
+      <c r="E23" t="n">
+        <v>486510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3737,10 +3723,8 @@
           <t>14500,18230,16250,14860</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y23" t="n">
+        <v>2</v>
       </c>
       <c r="Z23" t="n">
         <v>14000</v>
@@ -3814,10 +3798,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E24" t="n">
+        <v>660</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3880,10 +3862,8 @@
           <t>1761000,1790000,1783000,1828000,1842000</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y24" t="n">
+        <v>-7</v>
       </c>
       <c r="Z24" t="n">
         <v>-331000</v>
@@ -3939,6 +3919,149 @@
       <c r="AQ24" t="inlineStr">
         <is>
           <t>오너리스크 및 솔리다임 상장 이슈로 인한 SK하이닉스 주가 하락 우려. HBM 경쟁력 약화 지적.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>158430</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>41</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>7010</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>+27.45%</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>17745433</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>118730817750</v>
+      </c>
+      <c r="R25" t="n">
+        <v>106.11</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="U25" t="n">
+        <v>122</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.3770309435287919</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>5660,5420,5330,5390,5690</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>-102000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>60.18</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="n">
+        <v>111.27</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>63</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>4240</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>11370</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>3300</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1716</v>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>양자암호, 보안 기업으로서의 잠재력 언급. 해킹 방어 및 우리은행 협력 사례 제시. 단기 변동성에 대한 의견도 존재.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3941,10 +3941,8 @@
           <t>아톤</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>158430</t>
-        </is>
+      <c r="E25" t="n">
+        <v>158430</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4007,10 +4005,8 @@
           <t>5660,5420,5330,5390,5690</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y25" t="n">
+        <v>3</v>
       </c>
       <c r="Z25" t="n">
         <v>-102000</v>
@@ -4062,6 +4058,737 @@
       <c r="AQ25" t="inlineStr">
         <is>
           <t>양자암호, 보안 기업으로서의 잠재력 언급. 해킹 방어 및 우리은행 협력 사례 제시. 단기 변동성에 대한 의견도 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>26</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>16920</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>+13.79%</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>14051997</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>229745776055</v>
+      </c>
+      <c r="R26" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U26" t="n">
+        <v>137</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9613353451527725</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>11290,11130,11180,11820,14870</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>-83000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>302</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>4975</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17590</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>6320</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1879</v>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>개인정보 유출 사고 증가 속 양자보안 기술 부각, 농협/KDB생명 공급 논의 등 긍정적 뉴스 다수 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>26</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="L27" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>272500</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>+0.18%</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>8830757</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2425812421250</v>
+      </c>
+      <c r="R27" t="n">
+        <v>111.39</v>
+      </c>
+      <c r="S27" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="U27" t="n">
+        <v>800</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.3799344409267923</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>275000,269500,274500,276000,273000</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>1377000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE27" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-56.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>90200</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>15931109</v>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 연관된 부정적 여론 속에서 소폭 상승했으나, 4개월간 30만원 돌파 실패. 매수 주체에 대한 의문 제기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>26</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="L28" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>80900</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>-0.74%</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1511262</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>124422884200</v>
+      </c>
+      <c r="R28" t="n">
+        <v>88.62</v>
+      </c>
+      <c r="S28" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U28" t="n">
+        <v>276</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.4626635737432047</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>80500,81900,82300,81400,81600</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="n">
+        <v>612.88</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>518214</v>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 발표에 따른 두산에너빌리티 주가 상승 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>26</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="L29" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>5070</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>+1.20%</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>36044626</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>198147080555</v>
+      </c>
+      <c r="R29" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U29" t="n">
+        <v>140</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.4915252865048233</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>4025,4115,4140,4400,5140</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>381000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-17.45</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="n">
+        <v>-13.34</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>947</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>8100</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>592</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>5713</v>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>2200억 규모 수주 계약 선주문 가능성 언급, 미 증시 호조 및 개인 물량 매도세 관찰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>26</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="L30" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1742000</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1366671</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2391615128000</v>
+      </c>
+      <c r="R30" t="n">
+        <v>128.67</v>
+      </c>
+      <c r="S30" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U30" t="n">
+        <v>800</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.6653979531421805</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1790000,1783000,1828000,1842000,1784000</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-57000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE30" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-24.48</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>403000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>12725177</v>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>외국인 매도세 지속 및 추세선 하향 돌파, 공매도 비판 및 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ30"/>
+  <dimension ref="A1:AQ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4080,10 +4080,8 @@
           <t>라온시큐어</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>042510</t>
-        </is>
+      <c r="E26" t="n">
+        <v>42510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4146,10 +4144,8 @@
           <t>11290,11130,11180,11820,14870</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y26" t="n">
+        <v>8</v>
       </c>
       <c r="Z26" t="n">
         <v>-83000</v>
@@ -4227,10 +4223,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E27" t="n">
+        <v>5930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4293,10 +4287,8 @@
           <t>275000,269500,274500,276000,273000</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y27" t="n">
+        <v>-1</v>
       </c>
       <c r="Z27" t="n">
         <v>1377000</v>
@@ -4374,10 +4366,8 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>034020</t>
-        </is>
+      <c r="E28" t="n">
+        <v>34020</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4440,10 +4430,8 @@
           <t>80500,81900,82300,81400,81600</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y28" t="n">
+        <v>3</v>
       </c>
       <c r="Z28" t="n">
         <v>-8000</v>
@@ -4521,10 +4509,8 @@
           <t>빛과전자</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>069540</t>
-        </is>
+      <c r="E29" t="n">
+        <v>69540</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4587,10 +4573,8 @@
           <t>4025,4115,4140,4400,5140</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y29" t="n">
+        <v>6</v>
       </c>
       <c r="Z29" t="n">
         <v>381000</v>
@@ -4664,10 +4648,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E30" t="n">
+        <v>660</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4730,10 +4712,8 @@
           <t>1790000,1783000,1828000,1842000,1784000</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y30" t="n">
+        <v>-7</v>
       </c>
       <c r="Z30" t="n">
         <v>-199000</v>
@@ -4789,6 +4769,737 @@
       <c r="AQ30" t="inlineStr">
         <is>
           <t>외국인 매도세 지속 및 추세선 하향 돌파, 공매도 비판 및 주가 하락에 대한 부정적 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>019170</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>24</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="L31" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>11220</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>+16.03%</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>2838522</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>30625078170</v>
+      </c>
+      <c r="R31" t="n">
+        <v>97.34</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U31" t="n">
+        <v>145</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2703709703547708</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>9030,9040,9300,9310,10090</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>-105000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>5267</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>15900</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>6310</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>5881</v>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>러시아 흑사병, 케냐 에볼라 등 전염병 확산 관련 뉴스가 부각되며 테마주로 언급. 일부는 급등 기대를 보이나, 사실 관계 확인이 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>24</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="L32" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>13630</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>+10.54%</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>16353656</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>220926540005</v>
+      </c>
+      <c r="R32" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U32" t="n">
+        <v>125</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.859589765278071</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>11570,12270,11940,11970,12380</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>-68000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>20850</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>4020</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>3142</v>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>한화파워향 가스터빈 블레이드 첫 납품 뉴스에 따른 상승 기대감과 함께, 원자력 발전 투자 가능성 언급. 주포 이탈 및 개미 털기 논란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>24</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="L33" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>46250</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-2.43%</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>971857</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>45173659075</v>
+      </c>
+      <c r="R33" t="n">
+        <v>96.31999999999999</v>
+      </c>
+      <c r="S33" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U33" t="n">
+        <v>378</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.9664433693090188</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>40950,41350,40200,40650,47150</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="n">
+        <v>-27.58</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>61604</v>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>FDA 승인 가능성 90% 이상이라는 분석과 함께 초대형 블록버스터 신약 기대감 언급. 공매도 세력에 대한 경계와 함께 시총 100조원 돌파 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>삼천당제약</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>000250</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>24</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="L34" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>244500</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>+1.45%</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>422606</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>102606950750</v>
+      </c>
+      <c r="R34" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U34" t="n">
+        <v>222</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.547678275290216</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>166300,172400,199400,210000,246500</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>-78000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="n">
+        <v>1091.52</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>224</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>11868</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1233000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>57354</v>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>아일리아 관련 기대감과 함께 경구용 인슐린 10조원대 L/O 예상, 캐나다 및 독일 계약 공시 가능성이 언급됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>삼표시멘트</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>038500</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>24</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="L35" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>7780</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>+15.26%</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>17611782</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>140394898230</v>
+      </c>
+      <c r="R35" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U35" t="n">
+        <v>162</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.349042845803105</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>6530,6490,6750,6850,6790</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>-631000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>378</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>7323</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>23500</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>2890</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>8396</v>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ35"/>
+  <dimension ref="A1:AQ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4791,10 +4791,8 @@
           <t>신풍제약</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>019170</t>
-        </is>
+      <c r="E31" t="n">
+        <v>19170</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4857,10 +4855,8 @@
           <t>9030,9040,9300,9310,10090</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y31" t="n">
+        <v>7</v>
       </c>
       <c r="Z31" t="n">
         <v>-105000</v>
@@ -4934,10 +4930,8 @@
           <t>삼미금속</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>012210</t>
-        </is>
+      <c r="E32" t="n">
+        <v>12210</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5000,10 +4994,8 @@
           <t>11570,12270,11940,11970,12380</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y32" t="n">
+        <v>4</v>
       </c>
       <c r="Z32" t="n">
         <v>-68000</v>
@@ -5081,10 +5073,8 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>028300</t>
-        </is>
+      <c r="E33" t="n">
+        <v>28300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5147,10 +5137,8 @@
           <t>40950,41350,40200,40650,47150</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y33" t="n">
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
         <v>-61000</v>
@@ -5228,10 +5216,8 @@
           <t>삼천당제약</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>000250</t>
-        </is>
+      <c r="E34" t="n">
+        <v>250</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5294,10 +5280,8 @@
           <t>166300,172400,199400,210000,246500</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y34" t="n">
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
         <v>-78000</v>
@@ -5375,10 +5359,8 @@
           <t>삼표시멘트</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>038500</t>
-        </is>
+      <c r="E35" t="n">
+        <v>38500</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5441,10 +5423,8 @@
           <t>6530,6490,6750,6850,6790</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y35" t="n">
+        <v>6</v>
       </c>
       <c r="Z35" t="n">
         <v>-631000</v>
@@ -5500,6 +5480,737 @@
       <c r="AQ35" t="inlineStr">
         <is>
           <t>정부의 용적률 상향 및 그린벨트 해제 발표와 함께 성수동 삼표타워 건설 시작. 만원 돌파 기대감 및 거래량 증가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>고영</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>098460</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>20</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L36" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>38700</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>+6.91%</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2781696</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>106805120475</v>
+      </c>
+      <c r="R36" t="n">
+        <v>135.78</v>
+      </c>
+      <c r="S36" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U36" t="n">
+        <v>80</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.368823229750382</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>30850,33950,34450,36600,35850</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>199000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>215</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>5079</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>15530</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>26395</v>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>JP모건 등 기관/외인 매수세 유입, 추세 긍정적 평가 및 4만원 안착 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>20</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L37" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>1739000</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>+0.93%</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1276011</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2219877233000</v>
+      </c>
+      <c r="R37" t="n">
+        <v>119.53</v>
+      </c>
+      <c r="S37" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="U37" t="n">
+        <v>800</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.4767218160831089</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>1783000,1828000,1842000,1784000,1715000</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE37" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>-24.61</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>403000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>12703262</v>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 솔리다임 상장 이슈 관련 언급. 자사주 매입 및 외인 매매 동향 주시. 일부 긍정적 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HLB제약</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>047920</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L38" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>13360</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>+6.28%</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>5646543</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>75862269930</v>
+      </c>
+      <c r="R38" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="U38" t="n">
+        <v>89</v>
+      </c>
+      <c r="V38" t="n">
+        <v>3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.3856762412022066</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>11630,11220,10040,13010,12550</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>-324000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>141</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>3816</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>22250</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>5820</v>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>유증 물량 정리 후 주가 상승 기대감, 바이오스텝 및 HLB 승인 관련 논의.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>20</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L39" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>45900</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>578322</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>26540289800</v>
+      </c>
+      <c r="R39" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="S39" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="U39" t="n">
+        <v>250</v>
+      </c>
+      <c r="V39" t="n">
+        <v>3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.4325808727199436</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>41350,40200,40650,47150,45750</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="n">
+        <v>-27.37</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>61138</v>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>HLB, 리보세라닙 병용요법 허가 기대감 속에서 공매도와의 관계 언급. 긍정적 차트 분석 및 우상향 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>삼천당제약</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>000250</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>20</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L40" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>230500</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-4.36%</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>157038</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>35669964250</v>
+      </c>
+      <c r="R40" t="n">
+        <v>108.87</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="U40" t="n">
+        <v>112</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.7944111776447106</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>172400,199400,210000,246500,238500</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="n">
+        <v>1029.02</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>224</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>11868</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1233000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>54069</v>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>삼천당제약, 아일리아 영업이익 전망 및 연기금 매수 동향. 릴레이 계약공시 및 공매도 금지 관련 긍정적 뉴스.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ40"/>
+  <dimension ref="A1:AQ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5502,10 +5502,8 @@
           <t>고영</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>098460</t>
-        </is>
+      <c r="E36" t="n">
+        <v>98460</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5568,10 +5566,8 @@
           <t>30850,33950,34450,36600,35850</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y36" t="n">
+        <v>5</v>
       </c>
       <c r="Z36" t="n">
         <v>199000</v>
@@ -5649,10 +5645,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E37" t="n">
+        <v>660</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5715,10 +5709,8 @@
           <t>1783000,1828000,1842000,1784000,1715000</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y37" t="n">
+        <v>1</v>
       </c>
       <c r="Z37" t="n">
         <v>-25000</v>
@@ -5796,10 +5788,8 @@
           <t>HLB제약</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>047920</t>
-        </is>
+      <c r="E38" t="n">
+        <v>47920</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5862,10 +5852,8 @@
           <t>11630,11220,10040,13010,12550</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y38" t="n">
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
         <v>-324000</v>
@@ -5939,10 +5927,8 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>028300</t>
-        </is>
+      <c r="E39" t="n">
+        <v>28300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6005,10 +5991,8 @@
           <t>41350,40200,40650,47150,45750</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y39" t="n">
+        <v>2</v>
       </c>
       <c r="Z39" t="n">
         <v>-12000</v>
@@ -6086,10 +6070,8 @@
           <t>삼천당제약</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>000250</t>
-        </is>
+      <c r="E40" t="n">
+        <v>250</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6152,10 +6134,8 @@
           <t>172400,199400,210000,246500,238500</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y40" t="n">
+        <v>3</v>
       </c>
       <c r="Z40" t="n">
         <v>5000</v>
@@ -6211,6 +6191,737 @@
       <c r="AQ40" t="inlineStr">
         <is>
           <t>삼천당제약, 아일리아 영업이익 전망 및 연기금 매수 동향. 릴레이 계약공시 및 공매도 금지 관련 긍정적 뉴스.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:02</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>덕산넵코어스</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>266690</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L41" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>14460</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>+4.86%</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>14844513</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>215499364710</v>
+      </c>
+      <c r="R41" t="n">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="U41" t="n">
+        <v>648</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.44048557464922</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>16830,16600,16310,15990,13280</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>-22000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>28700</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>11600</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>2732</v>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>국민권익위 접수 사실 언급. 사기 상장 및 무차별 공매도에 대한 불만 제기. 인공위성 교신 성공 관련 내용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:02</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>20</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L42" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>264500</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>-1.49%</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>14919032</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3975645928750</v>
+      </c>
+      <c r="R42" t="n">
+        <v>89.37</v>
+      </c>
+      <c r="S42" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U42" t="n">
+        <v>800</v>
+      </c>
+      <c r="V42" t="n">
+        <v>8</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.5166412107188778</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>269500,274500,276000,273000,269000</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>56000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-965000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE42" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>-57.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>90200</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>15463407</v>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>영업이익 세계 최고에도 불구하고 주가 부양책 부재 및 정치적 이슈로 인한 투자 심리 위축.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:02</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>국제약품</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>002720</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>20</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L43" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>4230</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>-4.51%</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>20300930</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>92087029443</v>
+      </c>
+      <c r="R43" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U43" t="n">
+        <v>140</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.06186763372620127</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>3220,3250,3305,3480,4430</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>-471000</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>269</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>4617</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>5470</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>2810</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>895</v>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>미국 항생제 회사 주가 폭등 속 전염병 관련 뉴스 언급. 국제약품의 대장주 여부 및 금일 시가 지지 여부에 관심.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:02</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>20</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L44" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>16740</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>-3.46%</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>2861418</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>48085814040</v>
+      </c>
+      <c r="R44" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="S44" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="U44" t="n">
+        <v>127</v>
+      </c>
+      <c r="V44" t="n">
+        <v>8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.4149659863945578</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>17730,17830,17690,17790,17220</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>-58000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>-32.68</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="n">
+        <v>-7.63</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>68786</v>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>연기금 및 자산운용사의 매매 동향 및 공매도 과열 종목 지정 가능성 언급, 주가 조작 및 지속 성장성 의문 제기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:02</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>20</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L45" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>18950</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>-3.02%</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>2602076</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>49584632080</v>
+      </c>
+      <c r="R45" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="S45" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U45" t="n">
+        <v>143</v>
+      </c>
+      <c r="V45" t="n">
+        <v>5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.221251081976904</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>19840,19740,19920,19740,19510</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>-449000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-78000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>281.28</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>-50.97</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>620</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>4857</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>35350</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>18440</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>166760</v>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>증권사 애널리스트들의 추천 및 조선주 폭락 원인에 대한 불신 표출. 5개월간의 주가 하락세와 폐업 가능성 우려.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ45"/>
+  <dimension ref="A1:AQ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6213,10 +6213,8 @@
           <t>덕산넵코어스</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>266690</t>
-        </is>
+      <c r="E41" t="n">
+        <v>266690</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6279,10 +6277,8 @@
           <t>16830,16600,16310,15990,13280</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y41" t="n">
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>-22000</v>
@@ -6360,10 +6356,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E42" t="n">
+        <v>5930</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6426,10 +6420,8 @@
           <t>269500,274500,276000,273000,269000</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y42" t="n">
+        <v>-7</v>
       </c>
       <c r="Z42" t="n">
         <v>56000</v>
@@ -6507,10 +6499,8 @@
           <t>국제약품</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>002720</t>
-        </is>
+      <c r="E43" t="n">
+        <v>2720</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6573,10 +6563,8 @@
           <t>3220,3250,3305,3480,4430</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y43" t="n">
+        <v>5</v>
       </c>
       <c r="Z43" t="n">
         <v>-471000</v>
@@ -6650,10 +6638,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E44" t="n">
+        <v>47040</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6716,10 +6702,8 @@
           <t>17730,17830,17690,17790,17220</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y44" t="n">
+        <v>-6</v>
       </c>
       <c r="Z44" t="n">
         <v>-58000</v>
@@ -6797,10 +6781,8 @@
           <t>삼성중공업</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>010140</t>
-        </is>
+      <c r="E45" t="n">
+        <v>10140</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6863,10 +6845,8 @@
           <t>19840,19740,19920,19740,19510</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y45" t="n">
+        <v>-8</v>
       </c>
       <c r="Z45" t="n">
         <v>-449000</v>
@@ -6922,6 +6902,741 @@
       <c r="AQ45" t="inlineStr">
         <is>
           <t>증권사 애널리스트들의 추천 및 조선주 폭락 원인에 대한 불신 표출. 5개월간의 주가 하락세와 폐업 가능성 우려.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>20</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L46" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>13700</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>+22.98%</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10960587</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>145106219305</v>
+      </c>
+      <c r="R46" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U46" t="n">
+        <v>97</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.564552815940315</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>12320,12250,11830,11380,11030</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>-487000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>405.51</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE46" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1715</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>6841</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>19380</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>3200</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>5105</v>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>자체 개발 특허 출원 소식에도 불구하고 외국인, 기관, 기타법인 매도세가 나타나며 주가 상승 동력에 대한 의문 제기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>삼표시멘트</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>038500</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>20</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L47" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>7800</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>+10.17%</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>11667150</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>88323350030</v>
+      </c>
+      <c r="R47" t="n">
+        <v>96.17</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="T47" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>99</v>
+      </c>
+      <c r="V47" t="n">
+        <v>3</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.176158447967012</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>6750,6850,6790,7830,6830</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>-136000</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>378</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>7323</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>23500</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>2890</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>8417</v>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>성수메가프로젝트 및 건설기초소재 대장주로서의 입지 강조. 불황 속 226억 투자 및 반도체 수요 겨냥. 공매도 쇼퀴즈 및 국토부 승인 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>20</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L48" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>255000</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>-2.67%</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>7453695</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1920329736500</v>
+      </c>
+      <c r="R48" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="S48" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="T48" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="U48" t="n">
+        <v>800</v>
+      </c>
+      <c r="V48" t="n">
+        <v>9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.3174104253886079</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>274500,276000,273000,269000,263000</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>-416000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>-81000</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>-58.73</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>90200</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>14908010</v>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>역대급 실적 발표에도 주가 부양 실패 및 외국인 투자자 이탈에 대한 우려. 한국 증시 전반에 대한 부정적 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>20</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L49" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>1630000</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>-3.03%</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1484942</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2423255840500</v>
+      </c>
+      <c r="R49" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="S49" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="T49" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="U49" t="n">
+        <v>800</v>
+      </c>
+      <c r="V49" t="n">
+        <v>9</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9585504787298509</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>1828000,1842000,1784000,1715000,1686000</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>-276000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>14000</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE49" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>-28.57</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>403000</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>11907026</v>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>SK하이닉스 주가 하락과 자회사 솔리다임 중복 상장 논란에 대한 비판.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L50" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>45200</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>708132</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>32178343250</v>
+      </c>
+      <c r="R50" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="S50" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="T50" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U50" t="n">
+        <v>385</v>
+      </c>
+      <c r="V50" t="n">
+        <v>4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.9037191518943344</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>40200,40650,47150,45750,46000</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>-115000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="n">
+        <v>-26.95</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>60206</v>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>HLB 간암 1차 치료제 리보세라닙 관련 FDA 재승인 서류 제출 공시 확인. 연말 30만 기대감 및 공매도 세력에 대한 비판.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ50"/>
+  <dimension ref="A1:AQ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6924,10 +6924,8 @@
           <t>금호건설</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>002990</t>
-        </is>
+      <c r="E46" t="n">
+        <v>2990</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6990,10 +6988,8 @@
           <t>12320,12250,11830,11380,11030</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y46" t="n">
+        <v>3</v>
       </c>
       <c r="Z46" t="n">
         <v>-487000</v>
@@ -7071,10 +7067,8 @@
           <t>삼표시멘트</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>038500</t>
-        </is>
+      <c r="E47" t="n">
+        <v>38500</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7137,10 +7131,8 @@
           <t>6750,6850,6790,7830,6830</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y47" t="n">
+        <v>3</v>
       </c>
       <c r="Z47" t="n">
         <v>-136000</v>
@@ -7218,10 +7210,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E48" t="n">
+        <v>5930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7284,10 +7274,8 @@
           <t>274500,276000,273000,269000,263000</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y48" t="n">
+        <v>-6</v>
       </c>
       <c r="Z48" t="n">
         <v>-416000</v>
@@ -7365,10 +7353,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E49" t="n">
+        <v>660</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7431,10 +7417,8 @@
           <t>1828000,1842000,1784000,1715000,1686000</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y49" t="n">
+        <v>-6</v>
       </c>
       <c r="Z49" t="n">
         <v>-276000</v>
@@ -7512,10 +7496,8 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>028300</t>
-        </is>
+      <c r="E50" t="n">
+        <v>28300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7578,10 +7560,8 @@
           <t>40200,40650,47150,45750,46000</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y50" t="n">
+        <v>8</v>
       </c>
       <c r="Z50" t="n">
         <v>-115000</v>
@@ -7637,6 +7617,594 @@
       <c r="AQ50" t="inlineStr">
         <is>
           <t>HLB 간암 1차 치료제 리보세라닙 관련 FDA 재승인 서류 제출 공시 확인. 연말 30만 기대감 및 공매도 세력에 대한 비판.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>20</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L51" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>16090</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>-3.48%</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>3870184</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>63249841905</v>
+      </c>
+      <c r="R51" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="S51" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U51" t="n">
+        <v>204</v>
+      </c>
+      <c r="V51" t="n">
+        <v>9</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.376170661531231</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>17830,17690,17790,17220,16610</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>624000</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-94000</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE51" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>-33.2</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>66115</v>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>계속되는 주가 하락에 대한 불만과 특정 세력(모간이, 대차 해지 세력)에 대한 비난.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>20</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L52" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>7800</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>-4.41%</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>3842161</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>30096920285</v>
+      </c>
+      <c r="R52" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="S52" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="T52" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U52" t="n">
+        <v>204</v>
+      </c>
+      <c r="V52" t="n">
+        <v>2</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.2268144054057616</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>8550,8570,8630,8260,8160</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>-1233000</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>-21.15</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE52" t="n">
+        <v>12500</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>-35.84</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>453</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>13208</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>17950</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>7700</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>LG디스플레이 실적 부진 및 기업 가치 하락 전망, 투자자 이탈.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>20</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L53" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>18050</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>-7.48%</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>3192239</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>58219000000</v>
+      </c>
+      <c r="R53" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="S53" t="n">
+        <v>27.61</v>
+      </c>
+      <c r="T53" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="U53" t="n">
+        <v>140</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.2132735219691742</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>19740,19920,19740,19510,18900</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>93000</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>23000</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>281.28</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE53" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>-52.64</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>실적 호조에도 불구하고 주가 하락 및 52주 신저가 기록. 공매도 관련 불만과 조선업 전반의 부정적 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>20</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L54" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>15800</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>-6.89%</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>5048425</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>81926191545</v>
+      </c>
+      <c r="R54" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="T54" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>154</v>
+      </c>
+      <c r="V54" t="n">
+        <v>9</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.1517422197399857</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>17100,17860,18780,17720,16970</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>68000</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>-56000</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="n">
+        <v>-65.29000000000001</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>24567</v>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>3분기 실적 서프라이즈 발표와 함께 광통신 테마 및 AI 관련 긍정적 전망. 유튜버 언급.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ54"/>
+  <dimension ref="A1:AQ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,10 +7639,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E51" t="n">
+        <v>47040</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7705,10 +7703,8 @@
           <t>17830,17690,17790,17220,16610</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="Y51" t="n">
+        <v>-5</v>
       </c>
       <c r="Z51" t="n">
         <v>624000</v>
@@ -7786,10 +7782,8 @@
           <t>LG디스플레이</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>034220</t>
-        </is>
+      <c r="E52" t="n">
+        <v>34220</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7852,10 +7846,8 @@
           <t>8550,8570,8630,8260,8160</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="Y52" t="n">
+        <v>-5</v>
       </c>
       <c r="Z52" t="n">
         <v>-1233000</v>
@@ -7933,10 +7925,8 @@
           <t>삼성중공업</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>010140</t>
-        </is>
+      <c r="E53" t="n">
+        <v>10140</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7999,10 +7989,8 @@
           <t>19740,19920,19740,19510,18900</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y53" t="n">
+        <v>-8</v>
       </c>
       <c r="Z53" t="n">
         <v>93000</v>
@@ -8080,10 +8068,8 @@
           <t>대한광통신</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>010170</t>
-        </is>
+      <c r="E54" t="n">
+        <v>10170</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -8146,10 +8132,8 @@
           <t>17100,17860,18780,17720,16970</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y54" t="n">
+        <v>2</v>
       </c>
       <c r="Z54" t="n">
         <v>68000</v>
@@ -8205,6 +8189,737 @@
       <c r="AQ54" t="inlineStr">
         <is>
           <t>3분기 실적 서프라이즈 발표와 함께 광통신 테마 및 AI 관련 긍정적 전망. 유튜버 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>20</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L55" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>18400</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>+12.54%</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>11865937</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>217679660070</v>
+      </c>
+      <c r="R55" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T55" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U55" t="n">
+        <v>126</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.663643858202803</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>11820,14870,16350,15510,16520</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="n">
+        <v>60.93</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>302</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>4975</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>19930</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>6320</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>2043</v>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>보안 기술 중요성 부각과 함께 신고가 경신 및 추가 상승 기대감. 해킹 관련 이슈 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>20</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L56" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>43600</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>-1.80%</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>501305</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>21626263050</v>
+      </c>
+      <c r="R56" t="n">
+        <v>107.21</v>
+      </c>
+      <c r="S56" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="U56" t="n">
+        <v>180</v>
+      </c>
+      <c r="V56" t="n">
+        <v>5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.2525421701160426</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>40650,47150,45750,46000,44600</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>58074</v>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>신약 승인 기대감 속 공매도 세력 경계 및 주가 상승 가능성 언급. 악재 발생 시 하락 가능성도 제기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>20</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L57" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>13070</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>-2.46%</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>12323265</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>172079661590</v>
+      </c>
+      <c r="R57" t="n">
+        <v>86.31999999999999</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="U57" t="n">
+        <v>135</v>
+      </c>
+      <c r="V57" t="n">
+        <v>2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.7249494949494949</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>12250,11830,11380,11030,13760</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>-76000</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>405.51</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE57" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1715</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>6841</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>19380</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>3200</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>4870</v>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>반도체 클러스터 투자 관련 언급과 함께 주가 부진에 대한 답답함 토로. 공매도 경계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>서산</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>079650</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>20</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L58" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>8780</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>+29.88%</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10417593</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>87161347450</v>
+      </c>
+      <c r="R58" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="U58" t="n">
+        <v>105</v>
+      </c>
+      <c r="V58" t="n">
+        <v>2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>5640,5640,5350,5230,6760</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>-105000</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="n">
+        <v>-179.18</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>3495</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>10300</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>952</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1756</v>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>호남 반도체 클러스터 및 지역 개발 수혜 기대감. 연상 랠리 및 대장주로서의 강세 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>덕산넵코어스</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>266690</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>20</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L59" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>13300</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>-0.82%</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>4167421</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>58401685315</v>
+      </c>
+      <c r="R59" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U59" t="n">
+        <v>155</v>
+      </c>
+      <c r="V59" t="n">
+        <v>3</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.032805115373923</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>16310,15990,13280,13290,13360</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>28700</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>11600</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>2513</v>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>주가 부양 시도와 매도세 충돌. 공매도 및 대차 관련 언급에도 상승 동력 부족.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ59"/>
+  <dimension ref="A1:AQ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8211,10 +8211,8 @@
           <t>라온시큐어</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>042510</t>
-        </is>
+      <c r="E55" t="n">
+        <v>42510</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -8277,10 +8275,8 @@
           <t>11820,14870,16350,15510,16520</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y55" t="n">
+        <v>5</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8358,10 +8354,8 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>028300</t>
-        </is>
+      <c r="E56" t="n">
+        <v>28300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -8424,10 +8418,8 @@
           <t>40650,47150,45750,46000,44600</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y56" t="n">
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>45000</v>
@@ -8505,10 +8497,8 @@
           <t>금호건설</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>002990</t>
-        </is>
+      <c r="E57" t="n">
+        <v>2990</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8571,10 +8561,8 @@
           <t>12250,11830,11380,11030,13760</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y57" t="n">
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
         <v>-76000</v>
@@ -8652,10 +8640,8 @@
           <t>서산</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>079650</t>
-        </is>
+      <c r="E58" t="n">
+        <v>79650</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8718,10 +8704,8 @@
           <t>5640,5640,5350,5230,6760</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Y58" t="n">
+        <v>10</v>
       </c>
       <c r="Z58" t="n">
         <v>-105000</v>
@@ -8795,10 +8779,8 @@
           <t>덕산넵코어스</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>266690</t>
-        </is>
+      <c r="E59" t="n">
+        <v>266690</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8861,10 +8843,8 @@
           <t>16310,15990,13280,13290,13360</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="Y59" t="n">
+        <v>-2</v>
       </c>
       <c r="Z59" t="n">
         <v>34000</v>
@@ -8920,6 +8900,729 @@
       <c r="AQ59" t="inlineStr">
         <is>
           <t>주가 부양 시도와 매도세 충돌. 공매도 및 대차 관련 언급에도 상승 동력 부족.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>롯데손해보험</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>000400</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>20</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L60" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>+7.30%</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>14093071</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>35168552968</v>
+      </c>
+      <c r="R60" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>128</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.5841931942919868</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>2230,2180,2245,2295,2350</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>-47000</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>41000</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>3280</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>1576</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>7758</v>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>신한금융의 100% 지분 인수 확정 및 시너지 효과 기대감에 따른 급등 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>국제약품</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>002720</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>20</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L61" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>4605</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>+18.23%</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>29974562</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>133013423309</v>
+      </c>
+      <c r="R61" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U61" t="n">
+        <v>180</v>
+      </c>
+      <c r="V61" t="n">
+        <v>4</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.2949665538029565</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>3305,3480,4430,4235,3850</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>-75000</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>269</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>4617</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>5470</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>2810</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>974</v>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>흑사병 테마 관련 치료제 기대감 속 수급 쏠림 및 차익 실현 움직임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>20</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L62" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>18230</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>4262748</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>75194653995</v>
+      </c>
+      <c r="R62" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="S62" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U62" t="n">
+        <v>126</v>
+      </c>
+      <c r="V62" t="n">
+        <v>7</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.6535814153581415</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>19920,19740,19510,18900,17880</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>843000</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>211000</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>281.28</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE62" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>-43.29</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>620</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>4857</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>35350</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>17210</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>160424</v>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>FLNG 매출 확대 전망 뉴스 및 기술적 반등 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>20</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L63" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>15870</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>-1.37%</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>4123029</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>64509696320</v>
+      </c>
+      <c r="R63" t="n">
+        <v>130.37</v>
+      </c>
+      <c r="S63" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U63" t="n">
+        <v>191</v>
+      </c>
+      <c r="V63" t="n">
+        <v>10</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.4750212585034014</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>17690,17790,17220,16610,15920</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>658000</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>60000</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE63" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>-37.72</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="n">
+        <v>-7.23</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>65211</v>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>금감원의 사모펀드 점검 및 공매도 관련 언급. 시세 조정 및 매집 가능성 제기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>녹십자엠에스</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>142280</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>20</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L64" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>3785</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>+2.02%</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>25583439</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>103077059727</v>
+      </c>
+      <c r="R64" t="n">
+        <v>88.61</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="U64" t="n">
+        <v>133</v>
+      </c>
+      <c r="V64" t="n">
+        <v>2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>2.808149196774789</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>3345,3345,4300,3675,3580</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>-70000</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>-18000</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>169</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>2040</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>6660</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>907</v>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>흑사병 테마 관련 언급과 함께 독감, 코로나 백신 관련 내용 혼재. 대세 상승 시작 주장.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ64"/>
+  <dimension ref="A1:AQ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8922,10 +8922,8 @@
           <t>롯데손해보험</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>000400</t>
-        </is>
+      <c r="E60" t="n">
+        <v>400</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8988,10 +8986,8 @@
           <t>2230,2180,2245,2295,2350</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Y60" t="n">
+        <v>9</v>
       </c>
       <c r="Z60" t="n">
         <v>-47000</v>
@@ -9065,10 +9061,8 @@
           <t>국제약품</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>002720</t>
-        </is>
+      <c r="E61" t="n">
+        <v>2720</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -9131,10 +9125,8 @@
           <t>3305,3480,4430,4235,3850</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y61" t="n">
+        <v>3</v>
       </c>
       <c r="Z61" t="n">
         <v>-75000</v>
@@ -9208,10 +9200,8 @@
           <t>삼성중공업</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>010140</t>
-        </is>
+      <c r="E62" t="n">
+        <v>10140</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -9274,10 +9264,8 @@
           <t>19920,19740,19510,18900,17880</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y62" t="n">
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
         <v>843000</v>
@@ -9355,10 +9343,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E63" t="n">
+        <v>47040</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -9421,10 +9407,8 @@
           <t>17690,17790,17220,16610,15920</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y63" t="n">
+        <v>1</v>
       </c>
       <c r="Z63" t="n">
         <v>658000</v>
@@ -9502,10 +9486,8 @@
           <t>녹십자엠에스</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>142280</t>
-        </is>
+      <c r="E64" t="n">
+        <v>142280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -9568,10 +9550,8 @@
           <t>3345,3345,4300,3675,3580</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y64" t="n">
+        <v>3</v>
       </c>
       <c r="Z64" t="n">
         <v>-70000</v>
@@ -9623,6 +9603,729 @@
       <c r="AQ64" t="inlineStr">
         <is>
           <t>흑사병 테마 관련 언급과 함께 독감, 코로나 백신 관련 내용 혼재. 대세 상승 시작 주장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>20</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L65" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>65600</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>+3.63%</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1280238</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>82839842550</v>
+      </c>
+      <c r="R65" t="n">
+        <v>151.37</v>
+      </c>
+      <c r="S65" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U65" t="n">
+        <v>126</v>
+      </c>
+      <c r="V65" t="n">
+        <v>2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>2.883976774982174</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>76700,71100,69800,68900,61400</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="n">
+        <v>496.97</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>420208</v>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>원전 관련 긍정적 뉴스에도 불구하고 주가 흐름이 부진하며, 외국계 증권사의 매도 움직임이 관찰됩니다. 신뢰도 저하에 대한 우려도 제기됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>396300</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>20</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L66" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>8810</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>+23.22%</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>20562639</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>172994058820</v>
+      </c>
+      <c r="R66" t="n">
+        <v>101.63</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="T66" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="U66" t="n">
+        <v>139</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
+        <v>4.634493348874211</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>5850,6110,6400,7230,7150</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>47000</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>96</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>2745</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>8970</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>2270</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>2334</v>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>인수합병 관련 기대감과 코스닥 편입 이슈로 인한 급등이 예상됩니다. 텐버거 가능성에 대한 언급이 있으며, 투자 주의 종목 지정 가능성도 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>서산</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>079650</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>20</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L67" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>7890</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>+20.09%</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>8532655</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>68112661795</v>
+      </c>
+      <c r="R67" t="n">
+        <v>103.11</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="T67" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="U67" t="n">
+        <v>94</v>
+      </c>
+      <c r="V67" t="n">
+        <v>3</v>
+      </c>
+      <c r="W67" t="n">
+        <v>2.355954181975362</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>5230,6760,8780,7300,6570</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="n">
+        <v>-161.02</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>3495</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>10300</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>952</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>1578</v>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>군공항 이전 이슈와 정치 테마 관련 기대감이 형성되고 있습니다. 신고가 돌파 시 추가 상승 가능성이 언급되며, 호남 관련주로도 주목받고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>20</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L68" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>215500</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>+2.62%</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>8463055</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1813294169750</v>
+      </c>
+      <c r="R68" t="n">
+        <v>106.93</v>
+      </c>
+      <c r="S68" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="T68" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="U68" t="n">
+        <v>800</v>
+      </c>
+      <c r="V68" t="n">
+        <v>11</v>
+      </c>
+      <c r="W68" t="n">
+        <v>2.388456099068264</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>263000,251000,234000,234500,207500</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>-684000</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>-108000</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE68" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>-66.39</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>12598730</v>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 노조 관련 언급이 많으며, 주가 하락 및 외인 매도에 대한 부정적 인식이 나타납니다. AI 관련 긍정적 언급도 일부 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>5</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>멜콘</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>20</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L69" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>18270</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>+4.58%</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>7453308</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>140946375255</v>
+      </c>
+      <c r="R69" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>147</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
+        <v>2.073616018845701</v>
+      </c>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="n">
+        <v>40.69</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>449</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>7955</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>28800</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>15780</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2302</v>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>반도체 테마와 공급망 확충 수혜주로 언급되며, 글로벌 파운드리 연내 착공 관련 호재가 있습니다. 단일 계좌 투자 주의 종목 지정 가능성도 제기됩니다.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ69"/>
+  <dimension ref="A1:AQ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9625,10 +9625,8 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>034020</t>
-        </is>
+      <c r="E65" t="n">
+        <v>34020</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9691,10 +9689,8 @@
           <t>76700,71100,69800,68900,61400</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y65" t="n">
+        <v>-3</v>
       </c>
       <c r="Z65" t="n">
         <v>50000</v>
@@ -9772,10 +9768,8 @@
           <t>HT로보틱스</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>396300</t>
-        </is>
+      <c r="E66" t="n">
+        <v>396300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9838,10 +9832,8 @@
           <t>5850,6110,6400,7230,7150</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y66" t="n">
+        <v>6</v>
       </c>
       <c r="Z66" t="n">
         <v>47000</v>
@@ -9919,10 +9911,8 @@
           <t>서산</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>079650</t>
-        </is>
+      <c r="E67" t="n">
+        <v>79650</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9985,10 +9975,8 @@
           <t>5230,6760,8780,7300,6570</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y67" t="n">
+        <v>7</v>
       </c>
       <c r="Z67" t="n">
         <v>-8000</v>
@@ -10062,10 +10050,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E68" t="n">
+        <v>5930</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -10128,10 +10114,8 @@
           <t>263000,251000,234000,234500,207500</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="Y68" t="n">
+        <v>-2</v>
       </c>
       <c r="Z68" t="n">
         <v>-684000</v>
@@ -10209,10 +10193,8 @@
           <t>멜콘</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>179880</t>
-        </is>
+      <c r="E69" t="n">
+        <v>179880</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -10271,10 +10253,8 @@
         <v>2.073616018845701</v>
       </c>
       <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y69" t="n">
+        <v>3</v>
       </c>
       <c r="Z69" t="n">
         <v>3000</v>
@@ -10326,6 +10306,733 @@
       <c r="AQ69" t="inlineStr">
         <is>
           <t>반도체 테마와 공급망 확충 수혜주로 언급되며, 글로벌 파운드리 연내 착공 관련 호재가 있습니다. 단일 계좌 투자 주의 종목 지정 가능성도 제기됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>20</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L70" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="n">
+        <v>41750</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>+2.45%</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>434373</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>18028246300</v>
+      </c>
+      <c r="R70" t="n">
+        <v>117.38</v>
+      </c>
+      <c r="S70" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="U70" t="n">
+        <v>299</v>
+      </c>
+      <c r="V70" t="n">
+        <v>6</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.725069844346884</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>46000,44600,44100,41900,40050</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>73000</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>55610</v>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>C1 발표 및 FDA 승인에 대한 기대감. 임상 결과 및 규제 관련 불확실성 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>20</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L71" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>1286500</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>+1.94%</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>3852395</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>4963461807500</v>
+      </c>
+      <c r="R71" t="n">
+        <v>106.98</v>
+      </c>
+      <c r="S71" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="T71" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="U71" t="n">
+        <v>800</v>
+      </c>
+      <c r="V71" t="n">
+        <v>11</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.6854078849491694</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>1686000,1605000,1456000,1425000,1238000</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>-543000</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>-18000</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE71" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>420500</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>9397784</v>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>솔리다임 상장 철회 요구와 함께 주가 폭락 및 반도체 업황 둔화 우려가 지속됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="n">
+        <v>20</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L72" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="n">
+        <v>14850</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>+1.23%</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>2500377</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>37592889345</v>
+      </c>
+      <c r="R72" t="n">
+        <v>86.03</v>
+      </c>
+      <c r="S72" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U72" t="n">
+        <v>263</v>
+      </c>
+      <c r="V72" t="n">
+        <v>11</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.3678356907576051</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>16610,15920,15970,15730,14290</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>-134000</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE72" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="n">
+        <v>-6.77</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>61020</v>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>주가 조작 의혹 제기 및 외인 보유율 관련 언급. 단일판매 공급계약 체결 공시 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>진코스텍</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>250030</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="n">
+        <v>20</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L73" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>15390</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>+3.01%</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>5235663</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>81287931570</v>
+      </c>
+      <c r="R73" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>262</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.4776484996938151</v>
+      </c>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>30800</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>9810</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>583</v>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>상장 사기 및 공모가 뻥튀기 의혹 제기. 경영진 사퇴 요구 및 주가 부진에 대한 불만 표출.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>5</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>20</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L74" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>20350</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>-1.93%</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>3658183</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>75236888120</v>
+      </c>
+      <c r="R74" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="S74" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U74" t="n">
+        <v>127</v>
+      </c>
+      <c r="V74" t="n">
+        <v>2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.712143705463183</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>15510,16520,17530,18110,20100</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>302</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>4975</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>22450</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>6320</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>2260</v>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>양자보안 및 금융권 해킹 증가 추세에 따른 수혜 기대감. 신규 납품 요청 및 연기금 매수 동향 확인.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ74"/>
+  <dimension ref="A1:AQ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10328,10 +10328,8 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>028300</t>
-        </is>
+      <c r="E70" t="n">
+        <v>28300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -10394,10 +10392,8 @@
           <t>46000,44600,44100,41900,40050</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y70" t="n">
+        <v>3</v>
       </c>
       <c r="Z70" t="n">
         <v>73000</v>
@@ -10475,10 +10471,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E71" t="n">
+        <v>660</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -10541,10 +10535,8 @@
           <t>1686000,1605000,1456000,1425000,1238000</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="Y71" t="n">
+        <v>-5</v>
       </c>
       <c r="Z71" t="n">
         <v>-543000</v>
@@ -10622,10 +10614,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E72" t="n">
+        <v>47040</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -10688,10 +10678,8 @@
           <t>16610,15920,15970,15730,14290</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y72" t="n">
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>-134000</v>
@@ -10769,10 +10757,8 @@
           <t>진코스텍</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>250030</t>
-        </is>
+      <c r="E73" t="n">
+        <v>250030</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -10831,10 +10817,8 @@
         <v>0.4776484996938151</v>
       </c>
       <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y73" t="n">
+        <v>-3</v>
       </c>
       <c r="Z73" t="n">
         <v>-2000</v>
@@ -10908,10 +10892,8 @@
           <t>라온시큐어</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>042510</t>
-        </is>
+      <c r="E74" t="n">
+        <v>42510</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10974,10 +10956,8 @@
           <t>15510,16520,17530,18110,20100</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y74" t="n">
+        <v>5</v>
       </c>
       <c r="Z74" t="n">
         <v>-49000</v>
@@ -11033,6 +11013,737 @@
       <c r="AQ74" t="inlineStr">
         <is>
           <t>양자보안 및 금융권 해킹 증가 추세에 따른 수혜 기대감. 신규 납품 요청 및 연기금 매수 동향 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>KBI동양철관</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>008970</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L75" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>1748</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>+29.96%</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>12873744</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>20381066184</v>
+      </c>
+      <c r="R75" t="n">
+        <v>84.47</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="U75" t="n">
+        <v>104</v>
+      </c>
+      <c r="V75" t="n">
+        <v>1</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>1290,1292,1311,1259,1339</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>918000</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="n">
+        <v>-49.94</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1363</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>2970</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>890</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1814</v>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 관련 뉴스 확인. 외인 매수세 유입에 따른 주가 상승 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="n">
+        <v>20</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L76" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>216500</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>+0.46%</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>8462800</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1808607644750</v>
+      </c>
+      <c r="R76" t="n">
+        <v>116.41</v>
+      </c>
+      <c r="S76" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U76" t="n">
+        <v>800</v>
+      </c>
+      <c r="V76" t="n">
+        <v>12</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.9212016557736568</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>251000,234000,234500,207500,217000</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>1715000</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>573000</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE76" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>-66.11</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>12657193</v>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>이재명 관련 정치적 발언 및 개인적인 매매 경험 공유. 악재 소진 후 반등 기대감 존재하나 구체적인 근거 부족.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>명신산업</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>20</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L77" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>9460</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>+11.95%</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>2233267</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>21420770950</v>
+      </c>
+      <c r="R77" t="n">
+        <v>74.54000000000001</v>
+      </c>
+      <c r="S77" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U77" t="n">
+        <v>81</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1</v>
+      </c>
+      <c r="W77" t="n">
+        <v>2.391516103692066</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>8260,8390,8650,7800,9240</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>-259000</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>1302</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>14406</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>14940</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>5390</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>4964</v>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>테슬라 로드스터 수혜주로서의 명신산업 언급. 공매도 및 프로그램 매매 관련 내용 포함. 단기 상승 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>20</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L78" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>1253000</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>-1.49%</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>1932377</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>2387413741000</v>
+      </c>
+      <c r="R78" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="S78" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="T78" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="U78" t="n">
+        <v>800</v>
+      </c>
+      <c r="V78" t="n">
+        <v>12</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0.8490333586050038</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>1605000,1456000,1425000,1238000,1265000</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>54000</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>59000</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE78" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>-62</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>465500</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>9153069</v>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>솔리다임 관련 논란 및 최태원 회장에 대한 비판적 의견 다수. 주가 하락에 대한 부정적 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>20</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L79" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>14770</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>1513209</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>21983125295</v>
+      </c>
+      <c r="R79" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="S79" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="T79" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U79" t="n">
+        <v>91</v>
+      </c>
+      <c r="V79" t="n">
+        <v>12</v>
+      </c>
+      <c r="W79" t="n">
+        <v>2.901226000462642</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>15920,15970,15730,14290,14800</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>32000</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>-29000</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE79" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>-28.25</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="n">
+        <v>-6.73</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>60691</v>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>대우건설, 정치적 이슈와 연관된 부정적 언급 다수. 뱅크런 및 주가 조작 의혹 제기, 외인 보유율 관련 언급.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ79"/>
+  <dimension ref="A1:AQ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11035,10 +11035,8 @@
           <t>KBI동양철관</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>008970</t>
-        </is>
+      <c r="E75" t="n">
+        <v>8970</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -11101,10 +11099,8 @@
           <t>1290,1292,1311,1259,1339</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y75" t="n">
+        <v>8</v>
       </c>
       <c r="Z75" t="n">
         <v>918000</v>
@@ -11178,10 +11174,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E76" t="n">
+        <v>5930</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -11244,10 +11238,8 @@
           <t>251000,234000,234500,207500,217000</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="Y76" t="n">
+        <v>-2</v>
       </c>
       <c r="Z76" t="n">
         <v>1715000</v>
@@ -11325,10 +11317,8 @@
           <t>명신산업</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>009900</t>
-        </is>
+      <c r="E77" t="n">
+        <v>9900</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -11391,10 +11381,8 @@
           <t>8260,8390,8650,7800,9240</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y77" t="n">
+        <v>2</v>
       </c>
       <c r="Z77" t="n">
         <v>-259000</v>
@@ -11472,10 +11460,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E78" t="n">
+        <v>660</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -11538,10 +11524,8 @@
           <t>1605000,1456000,1425000,1238000,1265000</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y78" t="n">
+        <v>-7</v>
       </c>
       <c r="Z78" t="n">
         <v>54000</v>
@@ -11619,10 +11603,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E79" t="n">
+        <v>47040</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -11685,10 +11667,8 @@
           <t>15920,15970,15730,14290,14800</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y79" t="n">
+        <v>-3</v>
       </c>
       <c r="Z79" t="n">
         <v>32000</v>
@@ -11744,6 +11724,153 @@
       <c r="AQ79" t="inlineStr">
         <is>
           <t>대우건설, 정치적 이슈와 연관된 부정적 언급 다수. 뱅크런 및 주가 조작 의혹 제기, 외인 보유율 관련 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-19 15:01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>396300</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="n">
+        <v>20</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L80" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>9060</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>+0.55%</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>16521478</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>149843100170</v>
+      </c>
+      <c r="R80" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U80" t="n">
+        <v>125</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.7931472321716224</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>6110,6400,7230,7150,8830</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>-235000</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>96</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>2745</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>2270</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>HT로보틱스, 시장 전반의 하락세 속에서 특별한 근거 없이 개인 투자자들의 혼란과 손실 경험이 주로 언급됨.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ80"/>
+  <dimension ref="A1:AQ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11746,10 +11746,8 @@
           <t>HT로보틱스</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>396300</t>
-        </is>
+      <c r="E80" t="n">
+        <v>396300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -11812,10 +11810,8 @@
           <t>6110,6400,7230,7150,8830</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y80" t="n">
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
         <v>-235000</v>
@@ -11871,6 +11867,737 @@
       <c r="AQ80" t="inlineStr">
         <is>
           <t>HT로보틱스, 시장 전반의 하락세 속에서 특별한 근거 없이 개인 투자자들의 혼란과 손실 경험이 주로 언급됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>20</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L81" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>42650</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>-0.70%</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>243294</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>10296714475</v>
+      </c>
+      <c r="R81" t="n">
+        <v>103.78</v>
+      </c>
+      <c r="S81" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U81" t="n">
+        <v>145</v>
+      </c>
+      <c r="V81" t="n">
+        <v>7</v>
+      </c>
+      <c r="W81" t="n">
+        <v>3.297077922077922</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>44100,41900,40050,41850,43250</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>-21000</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="n">
+        <v>-25.43</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>56809</v>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>C1 발표 및 FDA 승인 관련 기대감이 있으나, 주가 상승 여부에 대한 불확실성 및 시장 신뢰 회복 필요성 등 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>396300</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="n">
+        <v>20</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L82" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>10240</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>+12.28%</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>17707313</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>189573589845</v>
+      </c>
+      <c r="R82" t="n">
+        <v>91.39</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T82" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="U82" t="n">
+        <v>167</v>
+      </c>
+      <c r="V82" t="n">
+        <v>3</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.1280009968709329</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>6400,7230,7150,8830,9140</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>325000</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="n">
+        <v>106.67</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>96</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>2745</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>11250</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2270</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>2713</v>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>로봇 및 ESS 사업의 강점과 수주잔고에 대한 긍정적 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:01</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>20</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L83" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>1244000</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>-2.58%</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>1965195</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>2405851039500</v>
+      </c>
+      <c r="R83" t="n">
+        <v>100.51</v>
+      </c>
+      <c r="S83" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="T83" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U83" t="n">
+        <v>800</v>
+      </c>
+      <c r="V83" t="n">
+        <v>13</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.609075563499156</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>1456000,1425000,1238000,1265000,1304000</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>-204000</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>-146000</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE83" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>-61.97</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>465500</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>9087325</v>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>솔리다임 상장 관련 불확실성 및 정치적 이슈 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:01</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>4</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>KBI동양철관</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>008970</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>20</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L84" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>1603</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>-8.30%</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>38184909</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>67602640358</v>
+      </c>
+      <c r="R84" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="U84" t="n">
+        <v>167</v>
+      </c>
+      <c r="V84" t="n">
+        <v>2</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.2323929571828731</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>1292,1311,1259,1339,1748</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>-457000</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="n">
+        <v>-45.8</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1363</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>2970</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>890</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1663</v>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>스페이스X 관련 호재 공시로 인한 급등세 기록. 3일간 코스피 수익률 3위 달성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:01</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>20</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L85" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>215000</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>-1.38%</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>6850940</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1470444721500</v>
+      </c>
+      <c r="R85" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="S85" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U85" t="n">
+        <v>800</v>
+      </c>
+      <c r="V85" t="n">
+        <v>13</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.5914491966652825</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>234000,234500,207500,217000,223500</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Z85" t="n">
+        <v>356000</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>-501000</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE85" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>-65.98999999999999</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>12569499</v>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 관련된 부정적 언급이 다수.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ85"/>
+  <dimension ref="A1:AQ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11889,10 +11889,8 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>028300</t>
-        </is>
+      <c r="E81" t="n">
+        <v>28300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -11955,10 +11953,8 @@
           <t>44100,41900,40050,41850,43250</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y81" t="n">
+        <v>3</v>
       </c>
       <c r="Z81" t="n">
         <v>-21000</v>
@@ -12036,10 +12032,8 @@
           <t>HT로보틱스</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>396300</t>
-        </is>
+      <c r="E82" t="n">
+        <v>396300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -12102,10 +12096,8 @@
           <t>6400,7230,7150,8830,9140</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y82" t="n">
+        <v>8</v>
       </c>
       <c r="Z82" t="n">
         <v>325000</v>
@@ -12183,10 +12175,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E83" t="n">
+        <v>660</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -12249,10 +12239,8 @@
           <t>1456000,1425000,1238000,1265000,1304000</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y83" t="n">
+        <v>-6</v>
       </c>
       <c r="Z83" t="n">
         <v>-204000</v>
@@ -12330,10 +12318,8 @@
           <t>KBI동양철관</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>008970</t>
-        </is>
+      <c r="E84" t="n">
+        <v>8970</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -12396,10 +12382,8 @@
           <t>1292,1311,1259,1339,1748</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y84" t="n">
+        <v>8</v>
       </c>
       <c r="Z84" t="n">
         <v>-457000</v>
@@ -12473,10 +12457,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E85" t="n">
+        <v>5930</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -12539,10 +12521,8 @@
           <t>234000,234500,207500,217000,223500</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y85" t="n">
+        <v>-7</v>
       </c>
       <c r="Z85" t="n">
         <v>356000</v>
@@ -12598,6 +12578,737 @@
       <c r="AQ85" t="inlineStr">
         <is>
           <t>정치적 이슈와 관련된 부정적 언급이 다수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>065450</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>20</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L86" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="n">
+        <v>3240</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>+11.15%</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>20118051</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>65252404350</v>
+      </c>
+      <c r="R86" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="T86" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>252</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0.1627891746754204</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>2845,2840,2675,2890,2985</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z86" t="n">
+        <v>-831000</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>103.56</v>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>154</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>2116</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>7050</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>956</v>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>김정은 사망설 등 지정학적 리스크 관련 루머 확산. 해당 루머를 통한 주가 변동 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:01</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>20</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L87" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="n">
+        <v>18250</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>-7.41%</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>5148133</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>104785913300</v>
+      </c>
+      <c r="R87" t="n">
+        <v>88.84</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="T87" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U87" t="n">
+        <v>139</v>
+      </c>
+      <c r="V87" t="n">
+        <v>3</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0.6549162418062636</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>17530,18110,20100,20800,19360</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z87" t="n">
+        <v>19000</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>302</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>4975</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>22450</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>6320</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>2027</v>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>주가 하락 및 매물대 형성, 개미 무덤 차트 패턴 언급. 기술력 부재 및 홍보성 상승에 대한 부정적 시각.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>브릴스</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>468670</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="n">
+        <v>20</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L88" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>16290</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>+0.56%</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>3996686</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>67218852160</v>
+      </c>
+      <c r="R88" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="S88" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="U88" t="n">
+        <v>195</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0.8651766402307137</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>19050,18940,14880,15460,16210</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z88" t="n">
+        <v>-69000</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>62100</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>14600</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>1851</v>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>종목 부진 및 보호예수 물량에 대한 우려 표출. 타 종목과의 비교 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>4</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>명신산업</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>20</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L89" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="n">
+        <v>8590</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>-11.63%</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>1993366</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>17994685805</v>
+      </c>
+      <c r="R89" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="S89" t="n">
+        <v>6</v>
+      </c>
+      <c r="T89" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="U89" t="n">
+        <v>167</v>
+      </c>
+      <c r="V89" t="n">
+        <v>2</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0.5426596969965447</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>8390,8650,7800,9240,9540</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z89" t="n">
+        <v>-181000</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>-535000</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1302</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>14406</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>14940</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>5390</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>4507</v>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>테슬라 부품 공급 관련 언급 및 주주환원 부족 지적. 공매도 관련 부정적 예측.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>5</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>272210</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>20</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L90" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>70700</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>-13.78%</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>1731808</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>125858473150</v>
+      </c>
+      <c r="R90" t="n">
+        <v>70.64</v>
+      </c>
+      <c r="S90" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="T90" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U90" t="n">
+        <v>269</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0.2895148669796557</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>77500,80700,73800,80500,81500</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z90" t="n">
+        <v>-628000</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>-70000</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>159.15</v>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE90" t="n">
+        <v>93000</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>-20.86</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1282</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>25933</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>184000</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>44750</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>133566</v>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ90"/>
+  <dimension ref="A1:AQ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12600,10 +12600,8 @@
           <t>빅텍</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>065450</t>
-        </is>
+      <c r="E86" t="n">
+        <v>65450</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -12666,10 +12664,8 @@
           <t>2845,2840,2675,2890,2985</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y86" t="n">
+        <v>5</v>
       </c>
       <c r="Z86" t="n">
         <v>-831000</v>
@@ -12747,10 +12743,8 @@
           <t>라온시큐어</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>042510</t>
-        </is>
+      <c r="E87" t="n">
+        <v>42510</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -12813,10 +12807,8 @@
           <t>17530,18110,20100,20800,19360</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y87" t="n">
+        <v>-6</v>
       </c>
       <c r="Z87" t="n">
         <v>19000</v>
@@ -12894,10 +12886,8 @@
           <t>브릴스</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>468670</t>
-        </is>
+      <c r="E88" t="n">
+        <v>468670</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -12960,10 +12950,8 @@
           <t>19050,18940,14880,15460,16210</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y88" t="n">
+        <v>-1</v>
       </c>
       <c r="Z88" t="n">
         <v>-69000</v>
@@ -13037,10 +13025,8 @@
           <t>명신산업</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>009900</t>
-        </is>
+      <c r="E89" t="n">
+        <v>9900</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -13103,10 +13089,8 @@
           <t>8390,8650,7800,9240,9540</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y89" t="n">
+        <v>-6</v>
       </c>
       <c r="Z89" t="n">
         <v>-181000</v>
@@ -13184,10 +13168,8 @@
           <t>한화시스템</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>272210</t>
-        </is>
+      <c r="E90" t="n">
+        <v>272210</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -13250,10 +13232,8 @@
           <t>77500,80700,73800,80500,81500</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y90" t="n">
+        <v>-8</v>
       </c>
       <c r="Z90" t="n">
         <v>-628000</v>
@@ -13309,6 +13289,741 @@
       <c r="AQ90" t="inlineStr">
         <is>
           <t>공매도 및 정치적 이슈로 인한 급락세. 이유 없는 하락에 대한 불만 표출.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>20</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L91" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="n">
+        <v>225500</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>+6.62%</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>9212018</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>2051921836000</v>
+      </c>
+      <c r="R91" t="n">
+        <v>135.72</v>
+      </c>
+      <c r="S91" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U91" t="n">
+        <v>800</v>
+      </c>
+      <c r="V91" t="n">
+        <v>14</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1.502552701470383</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>234500,207500,217000,223500,209000</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z91" t="n">
+        <v>1981000</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>380000</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE91" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>-64.92</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>13183358</v>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>외인 순매수세 유입 및 반도체 관련 지정학적 이슈 부각. 4분기 실적 개선 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>396300</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="n">
+        <v>20</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L92" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>11140</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>+14.02%</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>21496398</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>233489055655</v>
+      </c>
+      <c r="R92" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U92" t="n">
+        <v>146</v>
+      </c>
+      <c r="V92" t="n">
+        <v>4</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1.574463479497805</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>7230,7150,8830,9140,9970</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>350000</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="n">
+        <v>116.04</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>96</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>2745</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>11690</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>2270</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>2951</v>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>인공지능 데이터센터 수주잔고 급증 및 시총 대비 높은 성장성. 연말 1조 돌파 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>20</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L93" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="n">
+        <v>14760</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>+4.24%</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>1457303</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>21313700480</v>
+      </c>
+      <c r="R93" t="n">
+        <v>139.48</v>
+      </c>
+      <c r="S93" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U93" t="n">
+        <v>86</v>
+      </c>
+      <c r="V93" t="n">
+        <v>14</v>
+      </c>
+      <c r="W93" t="n">
+        <v>3.021615737500972</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>15730,14290,14800,15040,13860</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z93" t="n">
+        <v>133000</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE93" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>-27.55</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>60650</v>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>기관 및 외국인 순매수 유입. 실적 개선 및 목표가 상향 가능성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>4</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>20</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L94" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>1296000</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>+5.97%</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>2328954</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>3021563540000</v>
+      </c>
+      <c r="R94" t="n">
+        <v>119.52</v>
+      </c>
+      <c r="S94" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="T94" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="U94" t="n">
+        <v>800</v>
+      </c>
+      <c r="V94" t="n">
+        <v>14</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0.1964193046185781</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>1425000,1238000,1265000,1304000,1190000</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z94" t="n">
+        <v>150000</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>73000</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE94" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>-59.69</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>468000</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>9467181</v>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>자사주 매입 종료 후 마이크론 파업 관련 속보와 함께 금융기관 매도세 관찰. 일부에서는 외인/기관 순매수를 긍정적 신호로 해석하나, 솔리다임 상장 관련 부정적 전망도 공존.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>5</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>명신산업</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="n">
+        <v>20</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L95" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>9520</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>+10.06%</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>2665040</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>24713797980</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T95" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="U95" t="n">
+        <v>84</v>
+      </c>
+      <c r="V95" t="n">
+        <v>3</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0.5107966033158108</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>8650,7800,9240,9540,8410</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z95" t="n">
+        <v>225000</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1302</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>14406</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>14940</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>5390</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>4995</v>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>나스닥 상장 철회 관련 불확실성 해소 기대감. 차기 성장 동력 확보 노력.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ95"/>
+  <dimension ref="A1:AQ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13311,10 +13311,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E91" t="n">
+        <v>5930</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -13377,10 +13375,8 @@
           <t>234500,207500,217000,223500,209000</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y91" t="n">
+        <v>4</v>
       </c>
       <c r="Z91" t="n">
         <v>1981000</v>
@@ -13458,10 +13454,8 @@
           <t>HT로보틱스</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>396300</t>
-        </is>
+      <c r="E92" t="n">
+        <v>396300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -13524,10 +13518,8 @@
           <t>7230,7150,8830,9140,9970</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y92" t="n">
+        <v>3</v>
       </c>
       <c r="Z92" t="n">
         <v>350000</v>
@@ -13605,10 +13597,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E93" t="n">
+        <v>47040</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -13671,10 +13661,8 @@
           <t>15730,14290,14800,15040,13860</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y93" t="n">
+        <v>2</v>
       </c>
       <c r="Z93" t="n">
         <v>133000</v>
@@ -13752,10 +13740,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E94" t="n">
+        <v>660</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -13818,10 +13804,8 @@
           <t>1425000,1238000,1265000,1304000,1190000</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y94" t="n">
+        <v>2</v>
       </c>
       <c r="Z94" t="n">
         <v>150000</v>
@@ -13899,10 +13883,8 @@
           <t>명신산업</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>009900</t>
-        </is>
+      <c r="E95" t="n">
+        <v>9900</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -13965,10 +13947,8 @@
           <t>8650,7800,9240,9540,8410</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y95" t="n">
+        <v>5</v>
       </c>
       <c r="Z95" t="n">
         <v>225000</v>
@@ -14024,6 +14004,296 @@
       <c r="AQ95" t="inlineStr">
         <is>
           <t>나스닥 상장 철회 관련 불확실성 해소 기대감. 차기 성장 동력 확보 노력.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>푸드나무</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>290720</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="n">
+        <v>20</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L96" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>1579</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>+3.88%</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>51853962</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>79873001418</v>
+      </c>
+      <c r="R96" t="n">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="U96" t="n">
+        <v>281</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0.5005321479997495</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>3320,3145,3230,2170,1520</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z96" t="n">
+        <v>-184000</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>-25.99</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>203.78</v>
+      </c>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1019</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>1115</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>602</v>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>주당 3500원 인수 관련 언급과 함께 주가 급등락 및 상장폐지 우려 제기. 거래량에 기반한 움직임 분석.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>20</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L97" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="n">
+        <v>63400</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>+0.96%</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>1385296</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>88304325500</v>
+      </c>
+      <c r="R97" t="n">
+        <v>112.76</v>
+      </c>
+      <c r="S97" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="T97" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U97" t="n">
+        <v>180</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1</v>
+      </c>
+      <c r="W97" t="n">
+        <v>1.40762980305743</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>68900,61400,64400,67100,61700</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="Z97" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>19000</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE97" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>-46.92</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="n">
+        <v>480.3</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>406116</v>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>원전 및 전력 섹터 상승 기대에도 불구하고 주가 하락에 대한 불만. 외국인 및 연기금 매매 동향 언급.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ97"/>
+  <dimension ref="A1:AQ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14026,10 +14026,8 @@
           <t>푸드나무</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>290720</t>
-        </is>
+      <c r="E96" t="n">
+        <v>290720</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -14092,10 +14090,8 @@
           <t>3320,3145,3230,2170,1520</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y96" t="n">
+        <v>-1</v>
       </c>
       <c r="Z96" t="n">
         <v>-184000</v>
@@ -14169,10 +14165,8 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>034020</t>
-        </is>
+      <c r="E97" t="n">
+        <v>34020</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -14235,10 +14229,8 @@
           <t>68900,61400,64400,67100,61700</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
+      <c r="Y97" t="n">
+        <v>-4</v>
       </c>
       <c r="Z97" t="n">
         <v>-13000</v>
@@ -14294,6 +14286,733 @@
       <c r="AQ97" t="inlineStr">
         <is>
           <t>원전 및 전력 섹터 상승 기대에도 불구하고 주가 하락에 대한 불만. 외국인 및 연기금 매매 동향 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="n">
+        <v>20</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L98" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="n">
+        <v>56000</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>+17.40%</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>8915730</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>489495545950</v>
+      </c>
+      <c r="R98" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="S98" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U98" t="n">
+        <v>275</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1</v>
+      </c>
+      <c r="W98" t="n">
+        <v>7.334861657799501</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>41750,43600,45300,43100,47800</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z98" t="n">
+        <v>1412000</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>410000</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE98" t="n">
+        <v>69000</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>-20.58</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>24187</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>67300</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>23150</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>109760</v>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A, 어닝 서프라이즈 및 주식 소각 결정, 전망 상향 공시. MSCI 편입 예상.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>065450</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
+        <v>20</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L99" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>3625</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>+17.31%</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>16842149</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>59622822991</v>
+      </c>
+      <c r="R99" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>223</v>
+      </c>
+      <c r="V99" t="n">
+        <v>3</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0.5260383258499037</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>2675,2890,2985,3225,3200</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z99" t="n">
+        <v>-28000</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>150000</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>103.56</v>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>154</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>2116</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>7050</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>1069</v>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>김정은 신변 이상설 및 전쟁 가능성 대두에 따른 급등. 단기적 테마주로서의 움직임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>유니켐</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>011330</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="n">
+        <v>20</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L100" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>7400</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>+11.11%</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>1065801</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>8205879180</v>
+      </c>
+      <c r="R100" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>94</v>
+      </c>
+      <c r="V100" t="n">
+        <v>1</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0.1939278174323917</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>5890,5940,6470,6550,6740</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z100" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="n">
+        <v>-10.82</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>-684</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>14436</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>8430</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>391</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>741</v>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>로봇 관련 촉각 센서 기술 개발 및 현대차 파트너십을 기반으로 한 높은 기대감 표출. 미국 기업 루미아 인수 관련 구체적인 인수 의향서 및 본계약 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>푸드나무</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>290720</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>20</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L101" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>1755</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>+9.01%</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10075130</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>17430798923</v>
+      </c>
+      <c r="R101" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T101" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="U101" t="n">
+        <v>88</v>
+      </c>
+      <c r="V101" t="n">
+        <v>2</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0.8020390250489501</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>3145,3230,2170,1520,1655</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z101" t="n">
+        <v>126000</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>-25.99</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>203.78</v>
+      </c>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1019</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>1115</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>670</v>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>푸드나무, 보호예수 해제 및 인수설 속 주가 변동성 확대. 주가 조작 의혹 제기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="n">
+        <v>20</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L102" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>41800</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>-1.30%</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>214813</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>8925952900</v>
+      </c>
+      <c r="R102" t="n">
+        <v>123.27</v>
+      </c>
+      <c r="S102" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="T102" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="U102" t="n">
+        <v>172</v>
+      </c>
+      <c r="V102" t="n">
+        <v>8</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0.9741591468416735</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>40050,41850,43250,42600,42300</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z102" t="n">
+        <v>18000</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="n">
+        <v>-24.93</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>55677</v>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>간암 치료제 CRL 수령 이후 클래스 1 또는 즉시 승인 기대감 표출. FDA 승인 요건 미충족 가능성에 대한 신중론과 긍정론 혼재.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ102"/>
+  <dimension ref="A1:AQ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14308,10 +14308,8 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>028050</t>
-        </is>
+      <c r="E98" t="n">
+        <v>28050</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -14374,10 +14372,8 @@
           <t>41750,43600,45300,43100,47800</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y98" t="n">
+        <v>7</v>
       </c>
       <c r="Z98" t="n">
         <v>1412000</v>
@@ -14455,10 +14451,8 @@
           <t>빅텍</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>065450</t>
-        </is>
+      <c r="E99" t="n">
+        <v>65450</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -14521,10 +14515,8 @@
           <t>2675,2890,2985,3225,3200</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y99" t="n">
+        <v>7</v>
       </c>
       <c r="Z99" t="n">
         <v>-28000</v>
@@ -14602,10 +14594,8 @@
           <t>유니켐</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>011330</t>
-        </is>
+      <c r="E100" t="n">
+        <v>11330</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -14668,10 +14658,8 @@
           <t>5890,5940,6470,6550,6740</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y100" t="n">
+        <v>8</v>
       </c>
       <c r="Z100" t="n">
         <v>38000</v>
@@ -14745,10 +14733,8 @@
           <t>푸드나무</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>290720</t>
-        </is>
+      <c r="E101" t="n">
+        <v>290720</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -14811,10 +14797,8 @@
           <t>3145,3230,2170,1520,1655</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y101" t="n">
+        <v>1</v>
       </c>
       <c r="Z101" t="n">
         <v>126000</v>
@@ -14888,10 +14872,8 @@
           <t>HLB</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>028300</t>
-        </is>
+      <c r="E102" t="n">
+        <v>28300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -14954,10 +14936,8 @@
           <t>40050,41850,43250,42600,42300</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y102" t="n">
+        <v>4</v>
       </c>
       <c r="Z102" t="n">
         <v>18000</v>
@@ -15013,6 +14993,741 @@
       <c r="AQ102" t="inlineStr">
         <is>
           <t>간암 치료제 CRL 수령 이후 클래스 1 또는 즉시 승인 기대감 표출. FDA 승인 요건 미충족 가능성에 대한 신중론과 긍정론 혼재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:02</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="n">
+        <v>20</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L103" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="n">
+        <v>14530</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>-1.62%</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>2784261</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>41538394660</v>
+      </c>
+      <c r="R103" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="S103" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="U103" t="n">
+        <v>148</v>
+      </c>
+      <c r="V103" t="n">
+        <v>15</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0.06029839913564872</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>14290,14800,15040,13860,14820</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z103" t="n">
+        <v>97000</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>-79000</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE103" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>-31.95</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>59702</v>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>실적 우량주 언급과 함께 외국인·연기금 매수세 포착. 정치 관련 언급 및 삼성E&amp;A와의 비교.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:02</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="n">
+        <v>20</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L104" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="n">
+        <v>7230</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>2675644</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>19348228220</v>
+      </c>
+      <c r="R104" t="n">
+        <v>75.33</v>
+      </c>
+      <c r="S104" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U104" t="n">
+        <v>195</v>
+      </c>
+      <c r="V104" t="n">
+        <v>3</v>
+      </c>
+      <c r="W104" t="n">
+        <v>1.094985583805472</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>7320,7500,7520,7230,7350</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z104" t="n">
+        <v>-80000</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>-92000</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>-21.15</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE104" t="n">
+        <v>10500</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>-31.43</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>453</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>13208</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>17950</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>7120</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>36150</v>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>적자에서 흑자 전환 및 순이익 증가 등 긍정적 실적 발표. 주가 상승 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:02</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="n">
+        <v>20</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L105" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>13400</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>-6.36%</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>8390813</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>118638626305</v>
+      </c>
+      <c r="R105" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="S105" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U105" t="n">
+        <v>152</v>
+      </c>
+      <c r="V105" t="n">
+        <v>2</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0.1531898718138238</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>12450,13540,13490,12450,14550</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z105" t="n">
+        <v>-354000</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>-155000</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="n">
+        <v>-55.37</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>1640</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>20835</v>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>EUV용 유리기판 제조 기술 확보 및 AI 광통신 관련 뉴스. 삼성 인수설 등으로 인한 기대감 형성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:02</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="n">
+        <v>20</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L106" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>214250</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>-4.14%</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>9378788</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2044572742000</v>
+      </c>
+      <c r="R106" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="S106" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U106" t="n">
+        <v>800</v>
+      </c>
+      <c r="V106" t="n">
+        <v>15</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0.3798935153657844</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>207500,217000,223500,209000,223500</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z106" t="n">
+        <v>-1112000</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>-410000</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE106" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>-64.20999999999999</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>12525652</v>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>현 정부의 정책 실패와 주가 하락에 대한 불만을 표출하며, 정치적 이슈에 대한 부정적 감정 확산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:02</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>5</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>명신산업</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="n">
+        <v>20</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L107" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>9930</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>-2.55%</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>1830592</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>18120241185</v>
+      </c>
+      <c r="R107" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U107" t="n">
+        <v>140</v>
+      </c>
+      <c r="V107" t="n">
+        <v>4</v>
+      </c>
+      <c r="W107" t="n">
+        <v>2.33367129676569</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>7800,9240,9540,8410,10060</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z107" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>1302</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>14406</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>14940</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>5390</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>5210</v>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>테슬라 실적 호조 및 스페이스X 관련 뉴스에 따른 긍정적 전망, 단기적 하락 국면에서의 저점 매수 기회 탐색.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ107"/>
+  <dimension ref="A1:AQ112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15015,10 +15015,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E103" t="n">
+        <v>47040</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -15081,10 +15079,8 @@
           <t>14290,14800,15040,13860,14820</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y103" t="n">
+        <v>-3</v>
       </c>
       <c r="Z103" t="n">
         <v>97000</v>
@@ -15162,10 +15158,8 @@
           <t>LG디스플레이</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>034220</t>
-        </is>
+      <c r="E104" t="n">
+        <v>34220</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -15228,10 +15222,8 @@
           <t>7320,7500,7520,7230,7350</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y104" t="n">
+        <v>2</v>
       </c>
       <c r="Z104" t="n">
         <v>-80000</v>
@@ -15309,10 +15301,8 @@
           <t>대한광통신</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>010170</t>
-        </is>
+      <c r="E105" t="n">
+        <v>10170</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -15375,10 +15365,8 @@
           <t>12450,13540,13490,12450,14550</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y105" t="n">
+        <v>2</v>
       </c>
       <c r="Z105" t="n">
         <v>-354000</v>
@@ -15456,10 +15444,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E106" t="n">
+        <v>5930</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -15522,10 +15508,8 @@
           <t>207500,217000,223500,209000,223500</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y106" t="n">
+        <v>-8</v>
       </c>
       <c r="Z106" t="n">
         <v>-1112000</v>
@@ -15603,10 +15587,8 @@
           <t>명신산업</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>009900</t>
-        </is>
+      <c r="E107" t="n">
+        <v>9900</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -15669,10 +15651,8 @@
           <t>7800,9240,9540,8410,10060</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y107" t="n">
+        <v>2</v>
       </c>
       <c r="Z107" t="n">
         <v>-10000</v>
@@ -15728,6 +15708,741 @@
       <c r="AQ107" t="inlineStr">
         <is>
           <t>테슬라 실적 호조 및 스페이스X 관련 뉴스에 따른 긍정적 전망, 단기적 하락 국면에서의 저점 매수 기회 탐색.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:02</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="n">
+        <v>20</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L108" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="n">
+        <v>60400</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>+9.03%</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>9065218</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>538283688350</v>
+      </c>
+      <c r="R108" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="S108" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="T108" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U108" t="n">
+        <v>284</v>
+      </c>
+      <c r="V108" t="n">
+        <v>2</v>
+      </c>
+      <c r="W108" t="n">
+        <v>5.465803053394295</v>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>43600,45300,43100,47800,56100</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z108" t="n">
+        <v>1319000</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE108" t="n">
+        <v>72000</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>-17.64</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>24187</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>67300</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>23150</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>118384</v>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>외인·기관의 대규모 자사주 매입 및 매각 자금 유입, MSCI 패시브 자금 유입 전망에 따른 주가 상승 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:02</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>065450</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="n">
+        <v>20</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L109" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="n">
+        <v>4215</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>+12.40%</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>31470378</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>133766458819</v>
+      </c>
+      <c r="R109" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>243</v>
+      </c>
+      <c r="V109" t="n">
+        <v>4</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0.2784321398291267</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>2890,2985,3225,3200,3760</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z109" t="n">
+        <v>-250000</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>103.56</v>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>154</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>2116</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>7050</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>1243</v>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>북한 이상 징후와 연계된 방산주 급등. 외인 매도세 및 전쟁 불안감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:02</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="n">
+        <v>20</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L110" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>1228000</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>1929557</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>2333791894000</v>
+      </c>
+      <c r="R110" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="S110" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="T110" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U110" t="n">
+        <v>800</v>
+      </c>
+      <c r="V110" t="n">
+        <v>16</v>
+      </c>
+      <c r="W110" t="n">
+        <v>13.26001669449082</v>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>1265000,1304000,1190000,1288000,1234000</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z110" t="n">
+        <v>-339000</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>94000</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE110" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>-62.84</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>468000</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>8970446</v>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>주주환원 발표 기대감 속 기관 매도세 관찰. 솔리다임 IPO 중단 이슈.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:02</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>4</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="n">
+        <v>20</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L111" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>13360</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>3922150</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>51530706235</v>
+      </c>
+      <c r="R111" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="S111" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T111" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="U111" t="n">
+        <v>84</v>
+      </c>
+      <c r="V111" t="n">
+        <v>3</v>
+      </c>
+      <c r="W111" t="n">
+        <v>3.175429852977822</v>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>13540,13490,12450,14550,13450</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z111" t="n">
+        <v>-159000</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="n">
+        <v>-55.21</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>1640</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>20773</v>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>EUV 유리기판 관련 기술성 부각, 삼성 인수설 및 외인 매수세 유입, SK하이닉스 반등에 따른 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:02</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>5</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="n">
+        <v>20</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L112" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="n">
+        <v>17290</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>2553904</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>46165909775</v>
+      </c>
+      <c r="R112" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="S112" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="U112" t="n">
+        <v>82</v>
+      </c>
+      <c r="V112" t="n">
+        <v>5</v>
+      </c>
+      <c r="W112" t="n">
+        <v>7.520286396181384</v>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>20800,19360,17520,17790,18300</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z112" t="n">
+        <v>-11000</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>302</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>4975</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>22450</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>6320</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>1920</v>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>미국 보안주 폭등 속 라온시큐어 주가 변동성. AI 보안 해킹 우려.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ112"/>
+  <dimension ref="A1:AQ117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15730,10 +15730,8 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>028050</t>
-        </is>
+      <c r="E108" t="n">
+        <v>28050</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -15796,10 +15794,8 @@
           <t>43600,45300,43100,47800,56100</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y108" t="n">
+        <v>6</v>
       </c>
       <c r="Z108" t="n">
         <v>1319000</v>
@@ -15877,10 +15873,8 @@
           <t>빅텍</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>065450</t>
-        </is>
+      <c r="E109" t="n">
+        <v>65450</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -15943,10 +15937,8 @@
           <t>2890,2985,3225,3200,3760</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y109" t="n">
+        <v>7</v>
       </c>
       <c r="Z109" t="n">
         <v>-250000</v>
@@ -16024,10 +16016,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E110" t="n">
+        <v>660</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -16090,10 +16080,8 @@
           <t>1265000,1304000,1190000,1288000,1234000</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y110" t="n">
+        <v>3</v>
       </c>
       <c r="Z110" t="n">
         <v>-339000</v>
@@ -16171,10 +16159,8 @@
           <t>대한광통신</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>010170</t>
-        </is>
+      <c r="E111" t="n">
+        <v>10170</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -16237,10 +16223,8 @@
           <t>13540,13490,12450,14550,13450</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y111" t="n">
+        <v>5</v>
       </c>
       <c r="Z111" t="n">
         <v>-159000</v>
@@ -16318,10 +16302,8 @@
           <t>라온시큐어</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>042510</t>
-        </is>
+      <c r="E112" t="n">
+        <v>42510</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -16384,10 +16366,8 @@
           <t>20800,19360,17520,17790,18300</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y112" t="n">
+        <v>1</v>
       </c>
       <c r="Z112" t="n">
         <v>-11000</v>
@@ -16443,6 +16423,733 @@
       <c r="AQ112" t="inlineStr">
         <is>
           <t>미국 보안주 폭등 속 라온시큐어 주가 변동성. AI 보안 해킹 우려.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:02</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="n">
+        <v>20</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L113" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="n">
+        <v>14620</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>+0.62%</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>2262367</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>32531846235</v>
+      </c>
+      <c r="R113" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="S113" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="T113" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U113" t="n">
+        <v>134</v>
+      </c>
+      <c r="V113" t="n">
+        <v>16</v>
+      </c>
+      <c r="W113" t="n">
+        <v>1.47741935483871</v>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>14800,15040,13860,14820,14370</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z113" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>71000</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE113" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>-33.73</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>60071</v>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>3분기 실적 부진 및 의도적 주가 하락에 대한 의혹 제기. 거래량 감소와 함께 부정적 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:02</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>진양산업</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>003780</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="n">
+        <v>20</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L114" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="n">
+        <v>5490</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>+29.79%</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>4534834</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>22284386779</v>
+      </c>
+      <c r="R114" t="n">
+        <v>93.11</v>
+      </c>
+      <c r="S114" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T114" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="U114" t="n">
+        <v>160</v>
+      </c>
+      <c r="V114" t="n">
+        <v>1</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>4255,4430,4340,4455,4295</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z114" t="n">
+        <v>-66000</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>534</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>5164</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>8020</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>3660</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>714</v>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>오세훈 전 시장 무죄 판결에 따른 대권주자 관련 기대감 상승. 10배 상승 및 10연상 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:02</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>앤로보틱스</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>138360</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>20</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L115" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>1910</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>+16.82%</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>44020423</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>80945264054</v>
+      </c>
+      <c r="R115" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="S115" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="T115" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="U115" t="n">
+        <v>151</v>
+      </c>
+      <c r="V115" t="n">
+        <v>2</v>
+      </c>
+      <c r="W115" t="n">
+        <v>1.321685991852084</v>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>1301,1300,1391,1684,1620</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z115" t="n">
+        <v>65000</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>112</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1087</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>735</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>휴머노이드 배터리 충전 상용화 및 CES 관련 로봇주 상승 기대. 외인 매수세 유입 및 물량 확보 움직임 관찰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:02</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>20</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L116" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>213750</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>13474974</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>2823544092250</v>
+      </c>
+      <c r="R116" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="S116" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="T116" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U116" t="n">
+        <v>800</v>
+      </c>
+      <c r="V116" t="n">
+        <v>16</v>
+      </c>
+      <c r="W116" t="n">
+        <v>1.02226129988562</v>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>217000,223500,209000,223500,214500</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z116" t="n">
+        <v>-837000</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>169000</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE116" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>-67.22</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>12496421</v>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>추세 전환 및 24만원 목표 전망. 나스닥 필라델피아 반도체주 동반 상승 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:02</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="n">
+        <v>20</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L117" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="n">
+        <v>59200</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>-3.90%</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>2330869</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>137155453450</v>
+      </c>
+      <c r="R117" t="n">
+        <v>100.09</v>
+      </c>
+      <c r="S117" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="T117" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U117" t="n">
+        <v>282</v>
+      </c>
+      <c r="V117" t="n">
+        <v>2</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.045183332515979</v>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>64400,67100,61700,63700,61300</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z117" t="n">
+        <v>-256000</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>-143000</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE117" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>-51.33</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="n">
+        <v>448.48</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>379212</v>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>코스피 지수 및 미 증시 폭락과 연계하여 부정적 전망. 공매도 물량 및 최악의 종목으로 언급.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ117"/>
+  <dimension ref="A1:AQ122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16445,10 +16445,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E113" t="n">
+        <v>47040</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -16511,10 +16509,8 @@
           <t>14800,15040,13860,14820,14370</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y113" t="n">
+        <v>-3</v>
       </c>
       <c r="Z113" t="n">
         <v>-36000</v>
@@ -16592,10 +16588,8 @@
           <t>진양산업</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>003780</t>
-        </is>
+      <c r="E114" t="n">
+        <v>3780</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -16658,10 +16652,8 @@
           <t>4255,4430,4340,4455,4295</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y114" t="n">
+        <v>6</v>
       </c>
       <c r="Z114" t="n">
         <v>-66000</v>
@@ -16735,10 +16727,8 @@
           <t>앤로보틱스</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>138360</t>
-        </is>
+      <c r="E115" t="n">
+        <v>138360</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -16801,10 +16791,8 @@
           <t>1301,1300,1391,1684,1620</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y115" t="n">
+        <v>2</v>
       </c>
       <c r="Z115" t="n">
         <v>65000</v>
@@ -16878,10 +16866,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E116" t="n">
+        <v>5930</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -16944,10 +16930,8 @@
           <t>217000,223500,209000,223500,214500</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y116" t="n">
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
         <v>-837000</v>
@@ -17025,10 +17009,8 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>034020</t>
-        </is>
+      <c r="E117" t="n">
+        <v>34020</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -17091,10 +17073,8 @@
           <t>64400,67100,61700,63700,61300</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y117" t="n">
+        <v>-6</v>
       </c>
       <c r="Z117" t="n">
         <v>-256000</v>
@@ -17150,6 +17130,737 @@
       <c r="AQ117" t="inlineStr">
         <is>
           <t>코스피 지수 및 미 증시 폭락과 연계하여 부정적 전망. 공매도 물량 및 최악의 종목으로 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>20</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L118" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="n">
+        <v>1278000</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>1381383</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1780789834000</v>
+      </c>
+      <c r="R118" t="n">
+        <v>109.57</v>
+      </c>
+      <c r="S118" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="T118" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U118" t="n">
+        <v>800</v>
+      </c>
+      <c r="V118" t="n">
+        <v>17</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>1304000,1190000,1288000,1234000,1263000</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z118" t="n">
+        <v>-46000</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE118" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>-59.91</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>501000</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>9335692</v>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>주가 부양 의지 부족 및 시장 조작 의혹 제기, 데이터센터 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:01</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>루닛</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>328130</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>20</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L119" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="n">
+        <v>14690</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>+30.00%</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>4149532</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>58783178625</v>
+      </c>
+      <c r="R119" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="S119" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="T119" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="U119" t="n">
+        <v>145</v>
+      </c>
+      <c r="V119" t="n">
+        <v>1</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>12900,12780,11670,11040,11240</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z119" t="n">
+        <v>336000</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>305000</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>-23.52</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="n">
+        <v>-19.33</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>-760</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>2196</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>49800</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>8180</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>10938</v>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>AI 신약 밸류체인 합류 및 임상 진입, 연기금 순매수 기반 상승 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:01</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>진양산업</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>003780</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>20</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L120" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="n">
+        <v>5860</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>+6.74%</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>6210497</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>37066871665</v>
+      </c>
+      <c r="R120" t="n">
+        <v>84.22</v>
+      </c>
+      <c r="S120" t="n">
+        <v>2</v>
+      </c>
+      <c r="T120" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="U120" t="n">
+        <v>119</v>
+      </c>
+      <c r="V120" t="n">
+        <v>2</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3128549303045947</v>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>4430,4340,4455,4295,5490</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z120" t="n">
+        <v>41000</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>534</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>5164</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>7400</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>3660</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>762</v>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>정치 테마주에 대한 부정적 전망 및 투자 경고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:01</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>20</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L121" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>213250</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>-1.04%</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>6234442</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1331953785750</v>
+      </c>
+      <c r="R121" t="n">
+        <v>92.01000000000001</v>
+      </c>
+      <c r="S121" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="T121" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U121" t="n">
+        <v>800</v>
+      </c>
+      <c r="V121" t="n">
+        <v>17</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.7637890287972191</v>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>223500,209000,223500,214500,213500</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z121" t="n">
+        <v>-645000</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>53000</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE121" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>-66.03</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>12467189</v>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>현 정부 정책 및 경제 운영에 대한 비판과 불만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>20</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L122" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="n">
+        <v>58900</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>2778835</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>163620655700</v>
+      </c>
+      <c r="R122" t="n">
+        <v>78.34</v>
+      </c>
+      <c r="S122" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U122" t="n">
+        <v>125</v>
+      </c>
+      <c r="V122" t="n">
+        <v>3</v>
+      </c>
+      <c r="W122" t="n">
+        <v>1.172098150100642</v>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>45300,43100,47800,56100,59100</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z122" t="n">
+        <v>352000</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>16000</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE122" t="n">
+        <v>76000</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-21.84</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr"/>
+      <c r="AJ122" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>24187</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>67300</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>23150</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>115444</v>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>공매도 세력에 대한 경고와 상승 기대감.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ122"/>
+  <dimension ref="A1:AQ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17152,10 +17152,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E118" t="n">
+        <v>660</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -17218,10 +17216,8 @@
           <t>1304000,1190000,1288000,1234000,1263000</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y118" t="n">
+        <v>-1</v>
       </c>
       <c r="Z118" t="n">
         <v>-46000</v>
@@ -17299,10 +17295,8 @@
           <t>루닛</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>328130</t>
-        </is>
+      <c r="E119" t="n">
+        <v>328130</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -17365,10 +17359,8 @@
           <t>12900,12780,11670,11040,11240</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y119" t="n">
+        <v>8</v>
       </c>
       <c r="Z119" t="n">
         <v>336000</v>
@@ -17446,10 +17438,8 @@
           <t>진양산업</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>003780</t>
-        </is>
+      <c r="E120" t="n">
+        <v>3780</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -17512,10 +17502,8 @@
           <t>4430,4340,4455,4295,5490</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y120" t="n">
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
         <v>41000</v>
@@ -17589,10 +17577,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E121" t="n">
+        <v>5930</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -17655,10 +17641,8 @@
           <t>223500,209000,223500,214500,213500</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="Y121" t="n">
+        <v>-2</v>
       </c>
       <c r="Z121" t="n">
         <v>-645000</v>
@@ -17736,10 +17720,8 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>028050</t>
-        </is>
+      <c r="E122" t="n">
+        <v>28050</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -17802,10 +17784,8 @@
           <t>45300,43100,47800,56100,59100</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y122" t="n">
+        <v>4</v>
       </c>
       <c r="Z122" t="n">
         <v>352000</v>
@@ -17861,6 +17841,300 @@
       <c r="AQ122" t="inlineStr">
         <is>
           <t>공매도 세력에 대한 경고와 상승 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>20</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L123" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>57800</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>-2.69%</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>1246256</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>72307294100</v>
+      </c>
+      <c r="R123" t="n">
+        <v>98.01000000000001</v>
+      </c>
+      <c r="S123" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="T123" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U123" t="n">
+        <v>185</v>
+      </c>
+      <c r="V123" t="n">
+        <v>3</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.641898522663979</v>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>67100,61700,63700,61300,58900</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z123" t="n">
+        <v>-72000</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>-151000</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE123" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>-51.08</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="inlineStr"/>
+      <c r="AJ123" t="n">
+        <v>437.88</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>370244</v>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>정치적 요인에 따른 주가 하락에 대한 불만이 많으며, 폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성에 대한 언급이 있으나 신뢰도가 낮음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:02</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>빅텍</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>065450</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>20</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L124" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>3075</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>-19.29%</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>7950503</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>26072812870</v>
+      </c>
+      <c r="R124" t="n">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>290</v>
+      </c>
+      <c r="V124" t="n">
+        <v>5</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.2427334089958784</v>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>2985,3225,3200,3760,3635</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z124" t="n">
+        <v>69000</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>-142000</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>103.56</v>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="inlineStr"/>
+      <c r="AJ124" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>154</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>2116</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>7050</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>907</v>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>지정학적 리스크 테마주 언급. 급락 및 부정적 전망 다수.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ124"/>
+  <dimension ref="A1:AQ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17863,10 +17863,8 @@
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>034020</t>
-        </is>
+      <c r="E123" t="n">
+        <v>34020</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -17929,10 +17927,8 @@
           <t>67100,61700,63700,61300,58900</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="Y123" t="n">
+        <v>-5</v>
       </c>
       <c r="Z123" t="n">
         <v>-72000</v>
@@ -18010,10 +18006,8 @@
           <t>빅텍</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>065450</t>
-        </is>
+      <c r="E124" t="n">
+        <v>65450</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -18076,10 +18070,8 @@
           <t>2985,3225,3200,3760,3635</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y124" t="n">
+        <v>-8</v>
       </c>
       <c r="Z124" t="n">
         <v>69000</v>
@@ -18135,6 +18127,741 @@
       <c r="AQ124" t="inlineStr">
         <is>
           <t>지정학적 리스크 테마주 언급. 급락 및 부정적 전망 다수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:03</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>나무가</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>190510</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>20</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L125" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="n">
+        <v>17090</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>+29.96%</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>1119215</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>18709123205</v>
+      </c>
+      <c r="R125" t="n">
+        <v>108.56</v>
+      </c>
+      <c r="S125" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="T125" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="U125" t="n">
+        <v>90</v>
+      </c>
+      <c r="V125" t="n">
+        <v>1</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>14080,14430,14070,13580,15530</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z125" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="inlineStr"/>
+      <c r="AJ125" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1700</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>12226</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>28600</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>11050</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>2407</v>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 나무가의 독점 공급 관련 호재 부각. 3분기 어닝 서프라이즈 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:03</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="n">
+        <v>20</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L126" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>1345000</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>+5.49%</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>1665310</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>2268080544500</v>
+      </c>
+      <c r="R126" t="n">
+        <v>112.38</v>
+      </c>
+      <c r="S126" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="T126" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="U126" t="n">
+        <v>800</v>
+      </c>
+      <c r="V126" t="n">
+        <v>18</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.5836975878258054</v>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>1190000,1288000,1234000,1263000,1290000</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z126" t="n">
+        <v>174000</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE126" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>-54.7</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="inlineStr"/>
+      <c r="AJ126" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>501000</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>9825122</v>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>실적 발표 후 매수 권고 및 앤트로픽 관련 HBM 수요 언급. 외국인, 기관의 쌍끌이 매수세가 유입되었으나, 시장 전반의 대세 하락장 우려와 함께 단기적 상승 후 하락 가능성도 제기됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:03</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>3</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="n">
+        <v>20</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L127" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="n">
+        <v>14690</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>+3.31%</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>2251467</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>33484509635</v>
+      </c>
+      <c r="R127" t="n">
+        <v>123.84</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="T127" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U127" t="n">
+        <v>107</v>
+      </c>
+      <c r="V127" t="n">
+        <v>18</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.925039872408294</v>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>13860,14820,14370,14570,14230</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z127" t="n">
+        <v>392000</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE127" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>-32.77</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="inlineStr"/>
+      <c r="AJ127" t="n">
+        <v>-6.69</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>60359</v>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>3분기 영업이익 223% 증가 확인. 외국인, 기관 프로그램 매수세 지속 관찰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:03</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>4</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="n">
+        <v>20</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L128" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="n">
+        <v>62400</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>+4.35%</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>2995215</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>186605410350</v>
+      </c>
+      <c r="R128" t="n">
+        <v>93.95999999999999</v>
+      </c>
+      <c r="S128" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U128" t="n">
+        <v>123</v>
+      </c>
+      <c r="V128" t="n">
+        <v>4</v>
+      </c>
+      <c r="W128" t="n">
+        <v>3.320155201342282</v>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>43100,47800,56100,59100,60100</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z128" t="n">
+        <v>195000</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE128" t="n">
+        <v>76000</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>-18.55</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="inlineStr"/>
+      <c r="AJ128" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>24187</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>67300</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>23150</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>122304</v>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>중동발 지정학적 리스크 속에서도 삼성그룹주 중 저평가 메리트 부각. MSCI 종목 편입 기대감과 함께 대형 수주 공시 가능성이 거론되며, 외인 매수세 유입 및 야간 선물 급등 등 긍정적 시그널이 다수 관찰됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:03</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>5</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>루닛</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>328130</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>20</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L129" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="n">
+        <v>14550</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>-0.95%</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>4637577</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>69681548395</v>
+      </c>
+      <c r="R129" t="n">
+        <v>103.53</v>
+      </c>
+      <c r="S129" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="U129" t="n">
+        <v>141</v>
+      </c>
+      <c r="V129" t="n">
+        <v>2</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.1860827664399093</v>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>12780,11670,11040,11240,14690</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z129" t="n">
+        <v>264000</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>67000</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>-23.52</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr"/>
+      <c r="AJ129" t="n">
+        <v>-19.14</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>-760</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>2196</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>49800</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>8180</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>10834</v>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>본격적인 상승 추세 진입 및 거래대금 폭증, 공매도 숏커버링 발생. 루닛스코프, AI 신약 개발 활용 등 기술적 확장성과 성장성이 부각되며, 해외 수출 및 파트너십 확대가 긍정적 요인으로 분석됨.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ129"/>
+  <dimension ref="A1:AQ132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18149,10 +18149,8 @@
           <t>나무가</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>190510</t>
-        </is>
+      <c r="E125" t="n">
+        <v>190510</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -18215,10 +18213,8 @@
           <t>14080,14430,14070,13580,15530</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y125" t="n">
+        <v>8</v>
       </c>
       <c r="Z125" t="n">
         <v>75000</v>
@@ -18296,10 +18292,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E126" t="n">
+        <v>660</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -18362,10 +18356,8 @@
           <t>1190000,1288000,1234000,1263000,1290000</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y126" t="n">
+        <v>3</v>
       </c>
       <c r="Z126" t="n">
         <v>174000</v>
@@ -18443,10 +18435,8 @@
           <t>대우건설</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>047040</t>
-        </is>
+      <c r="E127" t="n">
+        <v>47040</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -18509,10 +18499,8 @@
           <t>13860,14820,14370,14570,14230</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y127" t="n">
+        <v>6</v>
       </c>
       <c r="Z127" t="n">
         <v>392000</v>
@@ -18590,10 +18578,8 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>028050</t>
-        </is>
+      <c r="E128" t="n">
+        <v>28050</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -18656,10 +18642,8 @@
           <t>43100,47800,56100,59100,60100</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y128" t="n">
+        <v>7</v>
       </c>
       <c r="Z128" t="n">
         <v>195000</v>
@@ -18737,10 +18721,8 @@
           <t>루닛</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>328130</t>
-        </is>
+      <c r="E129" t="n">
+        <v>328130</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -18803,10 +18785,8 @@
           <t>12780,11670,11040,11240,14690</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y129" t="n">
+        <v>6</v>
       </c>
       <c r="Z129" t="n">
         <v>264000</v>
@@ -18862,6 +18842,443 @@
       <c r="AQ129" t="inlineStr">
         <is>
           <t>본격적인 상승 추세 진입 및 거래대금 폭증, 공매도 숏커버링 발생. 루닛스코프, AI 신약 개발 활용 등 기술적 확장성과 성장성이 부각되며, 해외 수출 및 파트너십 확대가 긍정적 요인으로 분석됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:02</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="n">
+        <v>20</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L130" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="n">
+        <v>222250</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>+4.34%</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>10962177</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>2443490314250</v>
+      </c>
+      <c r="R130" t="n">
+        <v>103.81</v>
+      </c>
+      <c r="S130" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="T130" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U130" t="n">
+        <v>800</v>
+      </c>
+      <c r="V130" t="n">
+        <v>18</v>
+      </c>
+      <c r="W130" t="n">
+        <v>1.360273592342968</v>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>209000,223500,214500,213500,213500</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z130" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>668000</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE130" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-55.35</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr"/>
+      <c r="AJ130" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>12993354</v>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>실적 및 주주환원 발표 기대감에도 불구하고 외인 매도세가 관측되며 주가 상승폭이 제한적인 모습. 공매도 세력에 대한 언급 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:02</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>앤로보틱스</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>138360</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="n">
+        <v>20</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L131" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="n">
+        <v>2105</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>+3.44%</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>24462262</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>52607621762</v>
+      </c>
+      <c r="R131" t="n">
+        <v>87.73</v>
+      </c>
+      <c r="S131" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="T131" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U131" t="n">
+        <v>126</v>
+      </c>
+      <c r="V131" t="n">
+        <v>4</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.7367346459834315</v>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>1391,1684,1620,1946,2040</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z131" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr"/>
+      <c r="AJ131" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>112</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1087</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>749</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1852</v>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>종가 관리 및 주가 흐름에 대한 긍정적 언급과 함께 삼성전자와의 연관성 언급. 변동성 수반 속 주가 상승 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:02</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="n">
+        <v>20</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L132" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="n">
+        <v>34850</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>-4.52%</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>3277456</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>119297412050</v>
+      </c>
+      <c r="R132" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="S132" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="U132" t="n">
+        <v>157</v>
+      </c>
+      <c r="V132" t="n">
+        <v>1</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.5692533621889009</v>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>42250,45150,41900,39350,36200</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z132" t="n">
+        <v>-393000</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr"/>
+      <c r="AJ132" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>406</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>3034</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>126600</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>15260</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>6269</v>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>실적 호조에도 불구하고 주가 하락 및 개인 물량 던지기 현상 지속. 금감원 및 정부의 시장 개입 촉구. 외인 매도세 관측.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ132"/>
+  <dimension ref="A1:AQ137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18864,10 +18864,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E130" t="n">
+        <v>5930</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -18930,10 +18928,8 @@
           <t>209000,223500,214500,213500,213500</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y130" t="n">
+        <v>-1</v>
       </c>
       <c r="Z130" t="n">
         <v>1197000</v>
@@ -19011,10 +19007,8 @@
           <t>앤로보틱스</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>138360</t>
-        </is>
+      <c r="E131" t="n">
+        <v>138360</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -19077,10 +19071,8 @@
           <t>1391,1684,1620,1946,2040</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y131" t="n">
+        <v>2</v>
       </c>
       <c r="Z131" t="n">
         <v>-35000</v>
@@ -19154,10 +19146,8 @@
           <t>RF머트리얼즈</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>327260</t>
-        </is>
+      <c r="E132" t="n">
+        <v>327260</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -19220,10 +19210,8 @@
           <t>42250,45150,41900,39350,36200</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y132" t="n">
+        <v>-6</v>
       </c>
       <c r="Z132" t="n">
         <v>-393000</v>
@@ -19279,6 +19267,733 @@
       <c r="AQ132" t="inlineStr">
         <is>
           <t>실적 호조에도 불구하고 주가 하락 및 개인 물량 던지기 현상 지속. 금감원 및 정부의 시장 개입 촉구. 외인 매도세 관측.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:02</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="n">
+        <v>20</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L133" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>1452000</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>+8.28%</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>2327094</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>3291510345000</v>
+      </c>
+      <c r="R133" t="n">
+        <v>114</v>
+      </c>
+      <c r="S133" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="T133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U133" t="n">
+        <v>800</v>
+      </c>
+      <c r="V133" t="n">
+        <v>19</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.851506639427988</v>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>1288000,1234000,1263000,1290000,1374000</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z133" t="n">
+        <v>53000</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>55000</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE133" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-54.5</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr"/>
+      <c r="AJ133" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>501000</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>10606749</v>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>2029년 완판 및 자사주 20조 취득 발표 기반 긍정적 전망. 반도체 업황 회복 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:02</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="n">
+        <v>20</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L134" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>14900</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>+8.76%</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>10015404</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>147728730850</v>
+      </c>
+      <c r="R134" t="n">
+        <v>108.31</v>
+      </c>
+      <c r="S134" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U134" t="n">
+        <v>125</v>
+      </c>
+      <c r="V134" t="n">
+        <v>5</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.7214481498401096</v>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>14550,13450,13690,13330,13940</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z134" t="n">
+        <v>247000</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr"/>
+      <c r="AJ134" t="n">
+        <v>-61.57</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>1760</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>23167</v>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>메타 유리기판 및 해상광통신 케이블 관련 뉴스 기반 상승 기대. 외인 프로그램 적극 매수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:02</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
+        <v>20</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L135" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="n">
+        <v>239500</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>+7.88%</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>9416129</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>2231587594000</v>
+      </c>
+      <c r="R135" t="n">
+        <v>142.38</v>
+      </c>
+      <c r="S135" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U135" t="n">
+        <v>800</v>
+      </c>
+      <c r="V135" t="n">
+        <v>19</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.201523283429062</v>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>223500,214500,213500,213500,225000</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z135" t="n">
+        <v>1304000</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>524000</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE135" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-53.1</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr"/>
+      <c r="AJ135" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>14001837</v>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>HBM4 점유율 경쟁 및 피봇 후 반등 기대감. 일부 감정적 발언 포함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:02</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>4</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="n">
+        <v>20</v>
+      </c>
+      <c r="K136" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L136" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="n">
+        <v>4195</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>+29.88%</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>38028871</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>149406142766</v>
+      </c>
+      <c r="R136" t="n">
+        <v>88.54000000000001</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="U136" t="n">
+        <v>105</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>3780,3535,3375,3220,3470</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z136" t="n">
+        <v>647000</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-17.45</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AD136" t="inlineStr"/>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr"/>
+      <c r="AJ136" t="n">
+        <v>-11.04</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>947</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>8100</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>592</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>4727</v>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>미국 광통신주 급등에 따른 기대감 및 상한가 기록. 일부 부정적 인식 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:02</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>5</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>멜콘</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="n">
+        <v>20</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L137" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="n">
+        <v>17900</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>+13.08%</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>12330070</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>211806854965</v>
+      </c>
+      <c r="R137" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="U137" t="n">
+        <v>126</v>
+      </c>
+      <c r="V137" t="n">
+        <v>2</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.7591220068415051</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>15390,13250,12130,11960,15830</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z137" t="n">
+        <v>-21000</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr"/>
+      <c r="AJ137" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>449</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>7955</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>28800</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>11550</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>2255</v>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스 기반 긍정적 전망. 적정 밸류에이션 언급.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ137"/>
+  <dimension ref="A1:AQ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19289,10 +19289,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E133" t="n">
+        <v>660</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -19355,10 +19353,8 @@
           <t>1288000,1234000,1263000,1290000,1374000</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y133" t="n">
+        <v>6</v>
       </c>
       <c r="Z133" t="n">
         <v>53000</v>
@@ -19436,10 +19432,8 @@
           <t>대한광통신</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>010170</t>
-        </is>
+      <c r="E134" t="n">
+        <v>10170</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -19502,10 +19496,8 @@
           <t>14550,13450,13690,13330,13940</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y134" t="n">
+        <v>7</v>
       </c>
       <c r="Z134" t="n">
         <v>247000</v>
@@ -19583,10 +19575,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E135" t="n">
+        <v>5930</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -19649,10 +19639,8 @@
           <t>223500,214500,213500,213500,225000</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y135" t="n">
+        <v>1</v>
       </c>
       <c r="Z135" t="n">
         <v>1304000</v>
@@ -19730,10 +19718,8 @@
           <t>빛과전자</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>069540</t>
-        </is>
+      <c r="E136" t="n">
+        <v>69540</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -19796,10 +19782,8 @@
           <t>3780,3535,3375,3220,3470</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y136" t="n">
+        <v>8</v>
       </c>
       <c r="Z136" t="n">
         <v>647000</v>
@@ -19873,10 +19857,8 @@
           <t>멜콘</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>179880</t>
-        </is>
+      <c r="E137" t="n">
+        <v>179880</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -19939,10 +19921,8 @@
           <t>15390,13250,12130,11960,15830</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y137" t="n">
+        <v>7</v>
       </c>
       <c r="Z137" t="n">
         <v>-21000</v>
@@ -19994,6 +19974,741 @@
       <c r="AQ137" t="inlineStr">
         <is>
           <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스 기반 긍정적 전망. 적정 밸류에이션 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:02</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>명신산업</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>20</v>
+      </c>
+      <c r="K138" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L138" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="n">
+        <v>9210</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>+6.72%</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>2970099</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>26647462770</v>
+      </c>
+      <c r="R138" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="U138" t="n">
+        <v>165</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1</v>
+      </c>
+      <c r="W138" t="n">
+        <v>4.405524629765781</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>10060,9830,9010,8730,8720</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z138" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr"/>
+      <c r="AJ138" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1302</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>14406</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>14940</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>5390</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>4832</v>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>테슬라 관련 사업 진출 및 상표 출원 소식으로 인한 주가 상승 기대. 공매도 세력과의 경쟁.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:02</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>나무가</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>190510</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>20</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L139" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="n">
+        <v>18390</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>+7.61%</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>2445713</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>46877527005</v>
+      </c>
+      <c r="R139" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="S139" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="U139" t="n">
+        <v>144</v>
+      </c>
+      <c r="V139" t="n">
+        <v>2</v>
+      </c>
+      <c r="W139" t="n">
+        <v>2.961672473867596</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>14430,14070,13580,15530,17090</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z139" t="n">
+        <v>-59000</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>58000</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr"/>
+      <c r="AJ139" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1700</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>12226</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>28600</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>11050</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>2590</v>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>로봇 및 AI 관련 사업 성장성 부각. 휴머노이드, 데이터센터 방열 시스템 등 신규 계약 수주 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:02</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>20</v>
+      </c>
+      <c r="K140" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L140" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="n">
+        <v>64000</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>+2.89%</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>3719815</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>237421781550</v>
+      </c>
+      <c r="R140" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="S140" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="U140" t="n">
+        <v>160</v>
+      </c>
+      <c r="V140" t="n">
+        <v>5</v>
+      </c>
+      <c r="W140" t="n">
+        <v>4.297507845671036</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>47800,56100,59100,60100,62800</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z140" t="n">
+        <v>773000</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE140" t="n">
+        <v>76000</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>-16.58</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr"/>
+      <c r="AJ140" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>24187</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>67300</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>23150</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>125440</v>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>최근 4일간 코스피 수익률 1위 달성 및 자사주 매입 지속. 공매도 세력에 대한 경계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:02</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>4</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>20</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L141" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="n">
+        <v>16480</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>+0.55%</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>3644560</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>60035921120</v>
+      </c>
+      <c r="R141" t="n">
+        <v>103.21</v>
+      </c>
+      <c r="S141" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U141" t="n">
+        <v>153</v>
+      </c>
+      <c r="V141" t="n">
+        <v>15</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.5336181041534127</v>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>17620,17220,16680,16220,16480</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z141" t="n">
+        <v>-260000</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>-133000</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>281.28</v>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE141" t="n">
+        <v>27000</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>-39.56</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr"/>
+      <c r="AJ141" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>620</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>4857</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>35350</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>16270</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>145024</v>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>주문량 대비 주가 부진 지속. 애널리스트 보고서 및 실적 발표에 대한 불신.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:02</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>5</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>삼기에너지솔루션즈</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>419050</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>20</v>
+      </c>
+      <c r="K142" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L142" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="n">
+        <v>2570</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>+4.90%</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>32705701</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>89219744477</v>
+      </c>
+      <c r="R142" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="U142" t="n">
+        <v>130</v>
+      </c>
+      <c r="V142" t="n">
+        <v>1</v>
+      </c>
+      <c r="W142" t="n">
+        <v>2.251646241082861</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>2565,2310,2240,2330,2490</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z142" t="n">
+        <v>-364000</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>223.66</v>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr"/>
+      <c r="AJ142" t="n">
+        <v>-16.47</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1122</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2965</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>865</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1470</v>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>거래량 증가 및 외국인 매수세 유입에 따른 주가 반등 가능성. 시세 분출 기간 진입 전망.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ142"/>
+  <dimension ref="A1:AQ147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19996,10 +19996,8 @@
           <t>명신산업</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>009900</t>
-        </is>
+      <c r="E138" t="n">
+        <v>9900</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -20062,10 +20060,8 @@
           <t>10060,9830,9010,8730,8720</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y138" t="n">
+        <v>2</v>
       </c>
       <c r="Z138" t="n">
         <v>1000</v>
@@ -20143,10 +20139,8 @@
           <t>나무가</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>190510</t>
-        </is>
+      <c r="E139" t="n">
+        <v>190510</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -20209,10 +20203,8 @@
           <t>14430,14070,13580,15530,17090</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y139" t="n">
+        <v>7</v>
       </c>
       <c r="Z139" t="n">
         <v>-59000</v>
@@ -20290,10 +20282,8 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>028050</t>
-        </is>
+      <c r="E140" t="n">
+        <v>28050</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -20356,10 +20346,8 @@
           <t>47800,56100,59100,60100,62800</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y140" t="n">
+        <v>6</v>
       </c>
       <c r="Z140" t="n">
         <v>773000</v>
@@ -20437,10 +20425,8 @@
           <t>삼성중공업</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>010140</t>
-        </is>
+      <c r="E141" t="n">
+        <v>10140</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -20503,10 +20489,8 @@
           <t>17620,17220,16680,16220,16480</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="Y141" t="n">
+        <v>-2</v>
       </c>
       <c r="Z141" t="n">
         <v>-260000</v>
@@ -20584,10 +20568,8 @@
           <t>삼기에너지솔루션즈</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>419050</t>
-        </is>
+      <c r="E142" t="n">
+        <v>419050</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -20650,10 +20632,8 @@
           <t>2565,2310,2240,2330,2490</t>
         </is>
       </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y142" t="n">
+        <v>5</v>
       </c>
       <c r="Z142" t="n">
         <v>-364000</v>
@@ -20709,6 +20689,737 @@
       <c r="AQ142" t="inlineStr">
         <is>
           <t>거래량 증가 및 외국인 매수세 유입에 따른 주가 반등 가능성. 시세 분출 기간 진입 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:01</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>006400</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>20</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L143" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="n">
+        <v>536000</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>+0.37%</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>795738</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>428235788000</v>
+      </c>
+      <c r="R143" t="n">
+        <v>97.16</v>
+      </c>
+      <c r="S143" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="T143" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U143" t="n">
+        <v>316</v>
+      </c>
+      <c r="V143" t="n">
+        <v>1</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.8015072167582067</v>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>515000,484500,484000,513000,533000</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z143" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE143" t="n">
+        <v>740000</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>-25.68</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr"/>
+      <c r="AJ143" t="n">
+        <v>-64.38</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>-8325</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>272485</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>723000</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>259000</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>431938</v>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>호실적 달성 및 컨센서스 상회. 전고체 배터리 상용화 기대감 및 미래 성장 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:01</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>20</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L144" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="n">
+        <v>1518000</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>+2.08%</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>3001672</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>4581260095000</v>
+      </c>
+      <c r="R144" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="S144" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U144" t="n">
+        <v>800</v>
+      </c>
+      <c r="V144" t="n">
+        <v>20</v>
+      </c>
+      <c r="W144" t="n">
+        <v>1.135437113090744</v>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>1234000,1263000,1290000,1374000,1508000</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z144" t="n">
+        <v>337000</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>-93000</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE144" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>-58.38</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr"/>
+      <c r="AJ144" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>501000</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>11088874</v>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>삼성전자와 차별화된 움직임 기대. 최태원 회장의 경영 능력 긍정 평가. 국장 내 SK하이닉스의 대장주 역할 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:01</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>20</v>
+      </c>
+      <c r="K145" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L145" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="n">
+        <v>63200</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>-1.56%</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>2217653</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>141123057350</v>
+      </c>
+      <c r="R145" t="n">
+        <v>84.94</v>
+      </c>
+      <c r="S145" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="U145" t="n">
+        <v>113</v>
+      </c>
+      <c r="V145" t="n">
+        <v>6</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0.5544871794871795</v>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>56100,59100,60100,62800,63400</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z145" t="n">
+        <v>408000</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>-60000</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE145" t="n">
+        <v>76000</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>-16.64</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr"/>
+      <c r="AJ145" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>24187</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>67300</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>23150</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>123872</v>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>자사주 매입 및 소각 관련 긍정적 신호 포착. 수소 에너지 사업 기대감과 함께 신고가 경신 가능성에 대한 전망 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>4</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>20</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L146" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>9002647</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>137001359395</v>
+      </c>
+      <c r="R146" t="n">
+        <v>87.78</v>
+      </c>
+      <c r="S146" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="U146" t="n">
+        <v>132</v>
+      </c>
+      <c r="V146" t="n">
+        <v>6</v>
+      </c>
+      <c r="W146" t="n">
+        <v>2.417558886509636</v>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>13450,13690,13330,13940,15090</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z146" t="n">
+        <v>-312000</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr"/>
+      <c r="AJ146" t="n">
+        <v>-61.98</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>1819</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>23323</v>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>메타 관련 뉴스 및 3분기 전망 긍정적. 루멘텀 인수설 및 미국장 광통신 섹터 급등 영향 기대. 연말 3만 목표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:01</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>5</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>005935</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>20</v>
+      </c>
+      <c r="K147" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L147" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="n">
+        <v>184000</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>-3.21%</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>5873626</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>1106114005250</v>
+      </c>
+      <c r="R147" t="n">
+        <v>105.83</v>
+      </c>
+      <c r="S147" t="n">
+        <v>75</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U147" t="n">
+        <v>133</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0.3830674590762173</v>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>166600,166200,165600,173400,192600</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Z147" t="n">
+        <v>-409000</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>-172000</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr"/>
+      <c r="AJ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>243500</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>71000</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1476363</v>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>오너 리스크와 초허접한 IR 언급. 주주환원 불확실성 및 증여세 관련 주가 누르기 의혹 제기. 우선주 매입 소각 기대.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ147"/>
+  <dimension ref="A1:AQ152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20711,10 +20711,8 @@
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>006400</t>
-        </is>
+      <c r="E143" t="n">
+        <v>6400</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -20777,10 +20775,8 @@
           <t>515000,484500,484000,513000,533000</t>
         </is>
       </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y143" t="n">
+        <v>5</v>
       </c>
       <c r="Z143" t="n">
         <v>-24000</v>
@@ -20858,10 +20854,8 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>000660</t>
-        </is>
+      <c r="E144" t="n">
+        <v>660</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -20924,10 +20918,8 @@
           <t>1234000,1263000,1290000,1374000,1508000</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y144" t="n">
+        <v>2</v>
       </c>
       <c r="Z144" t="n">
         <v>337000</v>
@@ -21005,10 +20997,8 @@
           <t>삼성E&amp;A</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>028050</t>
-        </is>
+      <c r="E145" t="n">
+        <v>28050</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -21071,10 +21061,8 @@
           <t>56100,59100,60100,62800,63400</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y145" t="n">
+        <v>7</v>
       </c>
       <c r="Z145" t="n">
         <v>408000</v>
@@ -21152,10 +21140,8 @@
           <t>대한광통신</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>010170</t>
-        </is>
+      <c r="E146" t="n">
+        <v>10170</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -21218,10 +21204,8 @@
           <t>13450,13690,13330,13940,15090</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y146" t="n">
+        <v>5</v>
       </c>
       <c r="Z146" t="n">
         <v>-312000</v>
@@ -21299,10 +21283,8 @@
           <t>삼성전자우</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>005935</t>
-        </is>
+      <c r="E147" t="n">
+        <v>5935</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -21365,10 +21347,8 @@
           <t>166600,166200,165600,173400,192600</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y147" t="n">
+        <v>-7</v>
       </c>
       <c r="Z147" t="n">
         <v>-409000</v>
@@ -21420,6 +21400,733 @@
       <c r="AQ147" t="inlineStr">
         <is>
           <t>오너 리스크와 초허접한 IR 언급. 주주환원 불확실성 및 증여세 관련 주가 누르기 의혹 제기. 우선주 매입 소각 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:01</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>한화비전</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>489790</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>20</v>
+      </c>
+      <c r="K148" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L148" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="n">
+        <v>49650</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>+23.51%</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>2213896</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>100796981550</v>
+      </c>
+      <c r="R148" t="n">
+        <v>111.49</v>
+      </c>
+      <c r="S148" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U148" t="n">
+        <v>175</v>
+      </c>
+      <c r="V148" t="n">
+        <v>1</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0.5013927576601671</v>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>38400,38300,37000,39100,40450</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z148" t="n">
+        <v>-250000</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>51000</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>136.84</v>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE148" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>-50.35</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr"/>
+      <c r="AJ148" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>903</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>17188</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>97900</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>30950</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>25067</v>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>어닝 서프라이즈급 실적 발표 및 하이브리드 본더 시장 장악 기대감. 역대급 실적 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:01</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="n">
+        <v>20</v>
+      </c>
+      <c r="K149" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L149" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="n">
+        <v>232500</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>-3.93%</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>21928386</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>5158891712750</v>
+      </c>
+      <c r="R149" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="S149" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U149" t="n">
+        <v>800</v>
+      </c>
+      <c r="V149" t="n">
+        <v>20</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1.390157316065103</v>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>214500,213500,213500,225000,245000</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z149" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>-328000</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE149" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>-50.7</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr"/>
+      <c r="AJ149" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>13592598</v>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>주주환원 결정 지연 및 경영진 관련 논란으로 인한 부정적 전망. 컨퍼런스콜 내용 비판.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>3</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>루닛</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>328130</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>20</v>
+      </c>
+      <c r="K150" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L150" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="n">
+        <v>14800</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>+2.85%</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>4145360</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>62351240820</v>
+      </c>
+      <c r="R150" t="n">
+        <v>79.27</v>
+      </c>
+      <c r="S150" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="T150" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U150" t="n">
+        <v>140</v>
+      </c>
+      <c r="V150" t="n">
+        <v>3</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.500487329434698</v>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>11040,11240,14690,15070,14760</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z150" t="n">
+        <v>-273000</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>-23.52</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr"/>
+      <c r="AJ150" t="n">
+        <v>-19.47</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>-760</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>2196</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>49800</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>8180</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>11020</v>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>의료 AI 관련 종목 강세 속에서도 개인 투자자들의 매도 압력 및 공매도 관련 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:01</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>4</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="n">
+        <v>20</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L151" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="n">
+        <v>4047</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>-3.53%</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>40764633</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>172891414455</v>
+      </c>
+      <c r="R151" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="S151" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1</v>
+      </c>
+      <c r="U151" t="n">
+        <v>125</v>
+      </c>
+      <c r="V151" t="n">
+        <v>2</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.625918757195086</v>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>3535,3375,3220,3470,4195</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Z151" t="n">
+        <v>-190000</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>-17.45</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr"/>
+      <c r="AJ151" t="n">
+        <v>-10.65</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>947</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>8100</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>592</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>4561</v>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>보호예수 물량 폭탄 및 주가 폭락 우려. 허위 기사 논란과 주포의 의도에 대한 불신.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:01</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>서산</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>079650</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="n">
+        <v>20</v>
+      </c>
+      <c r="K152" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L152" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="n">
+        <v>7820</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>+4.97%</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>13248961</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>114157174025</v>
+      </c>
+      <c r="R152" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="T152" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="U152" t="n">
+        <v>231</v>
+      </c>
+      <c r="V152" t="n">
+        <v>1</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0.1751081640331076</v>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>7070,7300,6920,7530,7510</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr"/>
+      <c r="AJ152" t="n">
+        <v>-159.59</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>3495</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>10300</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>952</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1564</v>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>광주 반도체 테마와 연계된 상승 기대감. 외국인 및 기타 법인 매수세 유입으로 인한 주가 상승 전망.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ152"/>
+  <dimension ref="A1:AQ157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21422,10 +21422,8 @@
           <t>한화비전</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>489790</t>
-        </is>
+      <c r="E148" t="n">
+        <v>489790</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -21488,10 +21486,8 @@
           <t>38400,38300,37000,39100,40450</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y148" t="n">
+        <v>8</v>
       </c>
       <c r="Z148" t="n">
         <v>-250000</v>
@@ -21569,10 +21565,8 @@
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>005930</t>
-        </is>
+      <c r="E149" t="n">
+        <v>5930</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -21635,10 +21629,8 @@
           <t>214500,213500,213500,225000,245000</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y149" t="n">
+        <v>-8</v>
       </c>
       <c r="Z149" t="n">
         <v>-800000</v>
@@ -21716,10 +21708,8 @@
           <t>루닛</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>328130</t>
-        </is>
+      <c r="E150" t="n">
+        <v>328130</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -21782,10 +21772,8 @@
           <t>11040,11240,14690,15070,14760</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="Y150" t="n">
+        <v>-5</v>
       </c>
       <c r="Z150" t="n">
         <v>-273000</v>
@@ -21863,10 +21851,8 @@
           <t>빛과전자</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>069540</t>
-        </is>
+      <c r="E151" t="n">
+        <v>69540</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -21929,10 +21915,8 @@
           <t>3535,3375,3220,3470,4195</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y151" t="n">
+        <v>-7</v>
       </c>
       <c r="Z151" t="n">
         <v>-190000</v>
@@ -22006,10 +21990,8 @@
           <t>서산</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>079650</t>
-        </is>
+      <c r="E152" t="n">
+        <v>79650</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -22072,10 +22054,8 @@
           <t>7070,7300,6920,7530,7510</t>
         </is>
       </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y152" t="n">
+        <v>7</v>
       </c>
       <c r="Z152" t="n">
         <v>0</v>
@@ -22127,6 +22107,733 @@
       <c r="AQ152" t="inlineStr">
         <is>
           <t>광주 반도체 테마와 연계된 상승 기대감. 외국인 및 기타 법인 매수세 유입으로 인한 주가 상승 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:03</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>한화비전</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>489790</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="n">
+        <v>20</v>
+      </c>
+      <c r="K153" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L153" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="n">
+        <v>50500</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>+2.85%</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>979986</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>49298801125</v>
+      </c>
+      <c r="R153" t="n">
+        <v>103.71</v>
+      </c>
+      <c r="S153" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="T153" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="U153" t="n">
+        <v>93</v>
+      </c>
+      <c r="V153" t="n">
+        <v>2</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0.999728433058749</v>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>38300,37000,39100,40450,49150</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z153" t="n">
+        <v>-37000</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>55000</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>136.84</v>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE153" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>-50.35</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr"/>
+      <c r="AJ153" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>903</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>17188</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>97900</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>30950</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>25497</v>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>사상 최대 실적 발표에도 불구하고 주가 부진. TC본더 매출 본격화 및 소부장 평균 PER 대비 저평가 분석.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:03</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="n">
+        <v>20</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L154" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="n">
+        <v>19300</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>+15.92%</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>5176714</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>97587508225</v>
+      </c>
+      <c r="R154" t="n">
+        <v>103.08</v>
+      </c>
+      <c r="S154" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T154" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="U154" t="n">
+        <v>94</v>
+      </c>
+      <c r="V154" t="n">
+        <v>2</v>
+      </c>
+      <c r="W154" t="n">
+        <v>5.748441312008675</v>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>16800,17110,18160,19280,16650</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z154" t="n">
+        <v>94000</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>17000</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="inlineStr"/>
+      <c r="AJ154" t="n">
+        <v>63.91</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>302</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>4975</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>22450</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>6320</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2143</v>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>양자 보안 관련 법 시행 및 해킹 사태로 인한 수혜 기대감. 보안 대장주로서의 상승 가능성 부각.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:03</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="n">
+        <v>20</v>
+      </c>
+      <c r="K155" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L155" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="n">
+        <v>15790</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>+0.45%</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>2459876</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>38755378765</v>
+      </c>
+      <c r="R155" t="n">
+        <v>138.93</v>
+      </c>
+      <c r="S155" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U155" t="n">
+        <v>103</v>
+      </c>
+      <c r="V155" t="n">
+        <v>17</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.291945693055683</v>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>16680,16220,16480,16570,15740</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z155" t="n">
+        <v>345000</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>281.28</v>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE155" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>-45.28</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr"/>
+      <c r="AJ155" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>620</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>4857</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>35350</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>15320</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>138952</v>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>미국 조선주 강세와 대비되는 국내 조선주 약세. 실적 서프라이즈 및 증권사 리포트 긍정 전망에도 불구하고 업황 둔화 우려.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:03</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>4</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>서울반도체</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>046890</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="n">
+        <v>20</v>
+      </c>
+      <c r="K156" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L156" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="n">
+        <v>12310</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>+9.91%</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>3272775</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>41970895065</v>
+      </c>
+      <c r="R156" t="n">
+        <v>85.38</v>
+      </c>
+      <c r="S156" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="T156" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="U156" t="n">
+        <v>256</v>
+      </c>
+      <c r="V156" t="n">
+        <v>1</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0.2203650884198517</v>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>8210,8000,8330,10630,11200</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z156" t="n">
+        <v>-275000</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>Marketperform</t>
+        </is>
+      </c>
+      <c r="AE156" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="inlineStr"/>
+      <c r="AJ156" t="n">
+        <v>-13.96</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>-882</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>10993</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>18960</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>5730</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>7177</v>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 시장 석권 기대. 기술 개발 관련 긍정적 평가 및 저가 매수 기회 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:03</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>5</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>420610</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="n">
+        <v>20</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L157" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="n">
+        <v>23100</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>+156.67%</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>21972377</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>426587473790</v>
+      </c>
+      <c r="R157" t="n">
+        <v>82.04000000000001</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>447</v>
+      </c>
+      <c r="V157" t="n">
+        <v>1</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.347204968944099</v>
+      </c>
+      <c r="X157" t="inlineStr"/>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z157" t="n">
+        <v>-169000</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>-89000</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr"/>
+      <c r="AJ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>23350</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>16450</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>2618</v>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>신규 상장 후 급등락 반복. 단기 차익 실현 및 기술적 분석 기반의 매매 관점.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-10.xlsx
+++ b/data/reports/monthly_research_2026-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ157"/>
+  <dimension ref="A1:AQ162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22129,10 +22129,8 @@
           <t>한화비전</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>489790</t>
-        </is>
+      <c r="E153" t="n">
+        <v>489790</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -22195,10 +22193,8 @@
           <t>38300,37000,39100,40450,49150</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y153" t="n">
+        <v>3</v>
       </c>
       <c r="Z153" t="n">
         <v>-37000</v>
@@ -22276,10 +22272,8 @@
           <t>라온시큐어</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>042510</t>
-        </is>
+      <c r="E154" t="n">
+        <v>42510</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -22342,10 +22336,8 @@
           <t>16800,17110,18160,19280,16650</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y154" t="n">
+        <v>6</v>
       </c>
       <c r="Z154" t="n">
         <v>94000</v>
@@ -22423,10 +22415,8 @@
           <t>삼성중공업</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>010140</t>
-        </is>
+      <c r="E155" t="n">
+        <v>10140</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -22489,10 +22479,8 @@
           <t>16680,16220,16480,16570,15740</t>
         </is>
       </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y155" t="n">
+        <v>2</v>
       </c>
       <c r="Z155" t="n">
         <v>345000</v>
@@ -22570,10 +22558,8 @@
           <t>서울반도체</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>046890</t>
-        </is>
+      <c r="E156" t="n">
+        <v>46890</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -22636,10 +22622,8 @@
           <t>8210,8000,8330,10630,11200</t>
         </is>
       </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y156" t="n">
+        <v>6</v>
       </c>
       <c r="Z156" t="n">
         <v>-275000</v>
@@ -22717,10 +22701,8 @@
           <t>인텔리빅스</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>420610</t>
-        </is>
+      <c r="E157" t="n">
+        <v>420610</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -22779,10 +22761,8 @@
         <v>1.347204968944099</v>
       </c>
       <c r="X157" t="inlineStr"/>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y157" t="n">
+        <v>1</v>
       </c>
       <c r="Z157" t="n">
         <v>-169000</v>
@@ -22834,6 +22814,737 @@
       <c r="AQ157" t="inlineStr">
         <is>
           <t>신규 상장 후 급등락 반복. 단기 차익 실현 및 기술적 분석 기반의 매매 관점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="n">
+        <v>20</v>
+      </c>
+      <c r="K158" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L158" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="n">
+        <v>53600</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>-5.47%</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>1970837</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>107042202000</v>
+      </c>
+      <c r="R158" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="S158" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="T158" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U158" t="n">
+        <v>393</v>
+      </c>
+      <c r="V158" t="n">
+        <v>5</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0.4342583818931816</v>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>58900,57700,59500,62000,56700</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z158" t="n">
+        <v>-281000</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>-89000</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE158" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="inlineStr"/>
+      <c r="AJ158" t="n">
+        <v>406.06</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>53400</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>343341</v>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식. 정부 정책 및 국내 증시 상황과의 연관성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>상지건설</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>042940</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>20</v>
+      </c>
+      <c r="K159" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L159" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="n">
+        <v>7050</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>+12.98%</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>5693374</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>41211234590</v>
+      </c>
+      <c r="R159" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="n">
+        <v>133</v>
+      </c>
+      <c r="V159" t="n">
+        <v>1</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0.2216160041569239</v>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>4895,4635,4690,4800,6240</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z159" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>-15.33</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>123.48</v>
+      </c>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="inlineStr"/>
+      <c r="AJ159" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>-2263</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>14581</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>16620</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>4600</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>481</v>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>건설업 부활에 대한 기대감과 함께 급등 및 연상에 대한 언급. 유증 성공 여부 및 주가 움직임에 대한 관심 표출.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="n">
+        <v>20</v>
+      </c>
+      <c r="K160" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L160" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="n">
+        <v>221750</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>-4.42%</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>15497661</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>3442219808250</v>
+      </c>
+      <c r="R160" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="S160" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="T160" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U160" t="n">
+        <v>800</v>
+      </c>
+      <c r="V160" t="n">
+        <v>21</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0.5336350438492534</v>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>213500,213500,225000,245000,230500</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z160" t="n">
+        <v>538000</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>241000</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE160" t="n">
+        <v>690000</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>-67.68000000000001</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI160" t="inlineStr"/>
+      <c r="AJ160" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>94500</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>12964123</v>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>이재용 경영 퇴출 요구 및 자사주 매입/소각 촉구. 정치적 발언과 함께 주가 부양 의지 부족 비판.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>4</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>009830</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="n">
+        <v>20</v>
+      </c>
+      <c r="K161" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L161" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>22350</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>-5.30%</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>4514756</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>99079452650</v>
+      </c>
+      <c r="R161" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="S161" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T161" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="U161" t="n">
+        <v>276</v>
+      </c>
+      <c r="V161" t="n">
+        <v>4</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0.4104375569735643</v>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>28400,26450,26150,26750,23300</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z161" t="n">
+        <v>-728000</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>-220000</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>183.71</v>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE161" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>-42.76</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" t="inlineStr"/>
+      <c r="AJ161" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>-3377</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>47898</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>59300</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>21100</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>50263</v>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>RE100 1조원 승인 및 미국 카터스빌 모듈 완판 소식에도 불구하고 주가 하락 및 유증에 대한 불만, 의도적 주가 누르기 의혹 제기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>5</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="n">
+        <v>20</v>
+      </c>
+      <c r="K162" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L162" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>1394000</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>-8.65%</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>2938491</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>4157137058500</v>
+      </c>
+      <c r="R162" t="n">
+        <v>75.86</v>
+      </c>
+      <c r="S162" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U162" t="n">
+        <v>800</v>
+      </c>
+      <c r="V162" t="n">
+        <v>21</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0.9435149908895146</v>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>1263000,1290000,1374000,1508000,1516000</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z162" t="n">
+        <v>-177000</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>-59000</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE162" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>-55.62</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr"/>
+      <c r="AJ162" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>501000</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>10183064</v>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>자사주 매입 및 AI 투자 확대 뉴스에 대한 기대감. 정치적 이슈와 함께 변동성 높은 주가 흐름.</t>
         </is>
       </c>
     </row>
